--- a/volunteersync/test/e2e/reports/selenium_e2e_report.xlsx
+++ b/volunteersync/test/e2e/reports/selenium_e2e_report.xlsx
@@ -20,7 +20,7 @@
     <t>Generated At</t>
   </si>
   <si>
-    <t>23/7/2026, 9:38:09 am</t>
+    <t>25/7/2026, 9:29:54 pm</t>
   </si>
   <si>
     <t>Suite</t>
@@ -142,7 +142,7 @@
     <t>Page title contains "VolunteerSync"</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:42.739Z</t>
+    <t>2026-07-25T15:59:34.643Z</t>
   </si>
   <si>
     <t>Mocked. Target URL: https://tamilarasan13092005.github.io/volunteersync/</t>
@@ -165,7 +165,7 @@
     <t>"Get Started" element is found in DOM</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:42.795Z</t>
+    <t>2026-07-25T15:59:34.688Z</t>
   </si>
   <si>
     <t>LND-SEL-03</t>
@@ -184,7 +184,7 @@
     <t>No critical JavaScript errors in console</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:42.830Z</t>
+    <t>2026-07-25T15:59:34.718Z</t>
   </si>
   <si>
     <t>LND-SEL-04</t>
@@ -200,7 +200,7 @@
     <t>Login screen elements are present</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:42.864Z</t>
+    <t>2026-07-25T15:59:34.749Z</t>
   </si>
   <si>
     <t>LND-SEL-05</t>
@@ -216,7 +216,7 @@
     <t>Register screen is loaded</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:42.892Z</t>
+    <t>2026-07-25T15:59:34.780Z</t>
   </si>
   <si>
     <t>LND-SEL-06</t>
@@ -233,7 +233,7 @@
     <t>Flutter canvas renders within 5 seconds</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:42.927Z</t>
+    <t>2026-07-25T15:59:34.811Z</t>
   </si>
   <si>
     <t>LND-SEL-07</t>
@@ -256,7 +256,7 @@
     <t>Page load time is under 8 seconds</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:42.954Z</t>
+    <t>2026-07-25T15:59:34.841Z</t>
   </si>
   <si>
     <t>LND-SEL-08</t>
@@ -271,7 +271,7 @@
     <t>Viewport meta tag is present</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:42.989Z</t>
+    <t>2026-07-25T15:59:34.872Z</t>
   </si>
   <si>
     <t>LND-SEL-09</t>
@@ -289,7 +289,7 @@
     <t>Page title tag is not empty</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.013Z</t>
+    <t>2026-07-25T15:59:34.902Z</t>
   </si>
   <si>
     <t>LND-SEL-10</t>
@@ -304,7 +304,7 @@
     <t>Meta description tag is present</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.044Z</t>
+    <t>2026-07-25T15:59:34.933Z</t>
   </si>
   <si>
     <t>LND-SEL-11</t>
@@ -321,7 +321,7 @@
     <t>Page behaves correctly for Performance capability #11</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.072Z</t>
+    <t>2026-07-25T15:59:34.964Z</t>
   </si>
   <si>
     <t>LND-SEL-12</t>
@@ -341,7 +341,7 @@
     <t>Page behaves correctly for Security capability #12</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.107Z</t>
+    <t>2026-07-25T15:59:34.995Z</t>
   </si>
   <si>
     <t>LND-SEL-13</t>
@@ -361,7 +361,7 @@
     <t>Page behaves correctly for Accessibility capability #13</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.129Z</t>
+    <t>2026-07-25T15:59:35.026Z</t>
   </si>
   <si>
     <t>LND-SEL-14</t>
@@ -378,7 +378,7 @@
     <t>Page behaves correctly for UI Visibility capability #14</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.155Z</t>
+    <t>2026-07-25T15:59:35.056Z</t>
   </si>
   <si>
     <t>LND-SEL-15</t>
@@ -398,7 +398,7 @@
     <t>Page behaves correctly for Functional capability #15</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.184Z</t>
+    <t>2026-07-25T15:59:35.087Z</t>
   </si>
   <si>
     <t>LND-SEL-16</t>
@@ -418,7 +418,7 @@
     <t>Page behaves correctly for Validation capability #16</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.211Z</t>
+    <t>2026-07-25T15:59:35.118Z</t>
   </si>
   <si>
     <t>LND-SEL-17</t>
@@ -438,7 +438,7 @@
     <t>Page behaves correctly for Responsive capability #17</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.241Z</t>
+    <t>2026-07-25T15:59:35.149Z</t>
   </si>
   <si>
     <t>LND-SEL-18</t>
@@ -455,7 +455,7 @@
     <t>Page behaves correctly for Performance capability #18</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.274Z</t>
+    <t>2026-07-25T15:59:35.180Z</t>
   </si>
   <si>
     <t>LND-SEL-19</t>
@@ -472,7 +472,7 @@
     <t>Page behaves correctly for Security capability #19</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.301Z</t>
+    <t>2026-07-25T15:59:35.212Z</t>
   </si>
   <si>
     <t>LND-SEL-20</t>
@@ -489,7 +489,7 @@
     <t>Page behaves correctly for Accessibility capability #20</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.329Z</t>
+    <t>2026-07-25T15:59:35.243Z</t>
   </si>
   <si>
     <t>LND-SEL-21</t>
@@ -506,7 +506,7 @@
     <t>Page behaves correctly for UI Visibility capability #21</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.365Z</t>
+    <t>2026-07-25T15:59:35.274Z</t>
   </si>
   <si>
     <t>LND-SEL-22</t>
@@ -523,7 +523,7 @@
     <t>Page behaves correctly for Functional capability #22</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.395Z</t>
+    <t>2026-07-25T15:59:35.305Z</t>
   </si>
   <si>
     <t>LND-SEL-23</t>
@@ -540,7 +540,7 @@
     <t>Page behaves correctly for Validation capability #23</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.427Z</t>
+    <t>2026-07-25T15:59:35.336Z</t>
   </si>
   <si>
     <t>LND-SEL-24</t>
@@ -557,7 +557,7 @@
     <t>Page behaves correctly for Responsive capability #24</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.461Z</t>
+    <t>2026-07-25T15:59:35.368Z</t>
   </si>
   <si>
     <t>LND-SEL-25</t>
@@ -574,7 +574,7 @@
     <t>Page behaves correctly for Performance capability #25</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.491Z</t>
+    <t>2026-07-25T15:59:35.399Z</t>
   </si>
   <si>
     <t>LND-SEL-26</t>
@@ -591,7 +591,7 @@
     <t>Page behaves correctly for Security capability #26</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.518Z</t>
+    <t>2026-07-25T15:59:35.429Z</t>
   </si>
   <si>
     <t>LND-SEL-27</t>
@@ -608,7 +608,7 @@
     <t>Page behaves correctly for Accessibility capability #27</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.545Z</t>
+    <t>2026-07-25T15:59:35.459Z</t>
   </si>
   <si>
     <t>LND-SEL-28</t>
@@ -625,7 +625,7 @@
     <t>Page behaves correctly for UI Visibility capability #28</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.573Z</t>
+    <t>2026-07-25T15:59:35.489Z</t>
   </si>
   <si>
     <t>LND-SEL-29</t>
@@ -642,7 +642,7 @@
     <t>Page behaves correctly for Functional capability #29</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.607Z</t>
+    <t>2026-07-25T15:59:35.520Z</t>
   </si>
   <si>
     <t>LND-SEL-30</t>
@@ -659,7 +659,7 @@
     <t>Page behaves correctly for Validation capability #30</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.637Z</t>
+    <t>2026-07-25T15:59:35.551Z</t>
   </si>
   <si>
     <t>LND-SEL-31</t>
@@ -676,7 +676,7 @@
     <t>Page behaves correctly for Responsive capability #31</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.670Z</t>
+    <t>2026-07-25T15:59:35.582Z</t>
   </si>
   <si>
     <t>LND-SEL-32</t>
@@ -693,7 +693,7 @@
     <t>Page behaves correctly for Performance capability #32</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.704Z</t>
+    <t>2026-07-25T15:59:35.627Z</t>
   </si>
   <si>
     <t>LND-SEL-33</t>
@@ -710,7 +710,7 @@
     <t>Page behaves correctly for Security capability #33</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.734Z</t>
+    <t>2026-07-25T15:59:35.674Z</t>
   </si>
   <si>
     <t>LND-SEL-34</t>
@@ -727,7 +727,7 @@
     <t>Page behaves correctly for Accessibility capability #34</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.767Z</t>
+    <t>2026-07-25T15:59:35.704Z</t>
   </si>
   <si>
     <t>LND-SEL-35</t>
@@ -744,7 +744,7 @@
     <t>Page behaves correctly for UI Visibility capability #35</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.802Z</t>
+    <t>2026-07-25T15:59:35.734Z</t>
   </si>
   <si>
     <t>LND-SEL-36</t>
@@ -761,7 +761,7 @@
     <t>Page behaves correctly for Functional capability #36</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.836Z</t>
+    <t>2026-07-25T15:59:35.765Z</t>
   </si>
   <si>
     <t>LOG-SEL-01</t>
@@ -777,7 +777,7 @@
     <t>Login form is rendered</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.865Z</t>
+    <t>2026-07-25T15:59:35.796Z</t>
   </si>
   <si>
     <t>LOG-SEL-02</t>
@@ -794,7 +794,7 @@
     <t>Validation errors displayed for empty submission</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.892Z</t>
+    <t>2026-07-25T15:59:35.826Z</t>
   </si>
   <si>
     <t>LOG-SEL-03</t>
@@ -811,7 +811,7 @@
     <t>Email format validation error is shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.927Z</t>
+    <t>2026-07-25T15:59:35.857Z</t>
   </si>
   <si>
     <t>LOG-SEL-04</t>
@@ -828,7 +828,7 @@
     <t>Password length validation error is shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.962Z</t>
+    <t>2026-07-25T15:59:35.903Z</t>
   </si>
   <si>
     <t>LOG-SEL-05</t>
@@ -844,7 +844,7 @@
     <t>Forgot Password route is loaded</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:43.996Z</t>
+    <t>2026-07-25T15:59:35.934Z</t>
   </si>
   <si>
     <t>LOG-SEL-06</t>
@@ -860,7 +860,7 @@
     <t>Register page is loaded</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.038Z</t>
+    <t>2026-07-25T15:59:35.964Z</t>
   </si>
   <si>
     <t>LOG-SEL-07</t>
@@ -878,7 +878,7 @@
     <t>Password toggle changes input type between text and password</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.072Z</t>
+    <t>2026-07-25T15:59:35.996Z</t>
   </si>
   <si>
     <t>LOG-SEL-08</t>
@@ -895,7 +895,7 @@
     <t>User is authenticated and redirected to dashboard</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.100Z</t>
+    <t>2026-07-25T15:59:36.026Z</t>
   </si>
   <si>
     <t>LOG-SEL-09</t>
@@ -912,7 +912,7 @@
     <t>Error notification is displayed for invalid credentials</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.135Z</t>
+    <t>2026-07-25T15:59:36.057Z</t>
   </si>
   <si>
     <t>LOG-SEL-10</t>
@@ -927,7 +927,7 @@
     <t>Email input has appropriate type attribute</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.169Z</t>
+    <t>2026-07-25T15:59:36.089Z</t>
   </si>
   <si>
     <t>LOG-SEL-11</t>
@@ -941,7 +941,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.204Z</t>
+    <t>2026-07-25T15:59:36.119Z</t>
   </si>
   <si>
     <t>LOG-SEL-12</t>
@@ -955,7 +955,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.233Z</t>
+    <t>2026-07-25T15:59:36.149Z</t>
   </si>
   <si>
     <t>LOG-SEL-13</t>
@@ -969,7 +969,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.258Z</t>
+    <t>2026-07-25T15:59:36.180Z</t>
   </si>
   <si>
     <t>LOG-SEL-14</t>
@@ -983,7 +983,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.328Z</t>
+    <t>2026-07-25T15:59:36.211Z</t>
   </si>
   <si>
     <t>LOG-SEL-15</t>
@@ -997,7 +997,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.385Z</t>
+    <t>2026-07-25T15:59:36.243Z</t>
   </si>
   <si>
     <t>LOG-SEL-16</t>
@@ -1011,7 +1011,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.414Z</t>
+    <t>2026-07-25T15:59:36.274Z</t>
   </si>
   <si>
     <t>LOG-SEL-17</t>
@@ -1025,7 +1025,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.447Z</t>
+    <t>2026-07-25T15:59:36.305Z</t>
   </si>
   <si>
     <t>LOG-SEL-18</t>
@@ -1039,7 +1039,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.475Z</t>
+    <t>2026-07-25T15:59:36.336Z</t>
   </si>
   <si>
     <t>LOG-SEL-19</t>
@@ -1053,7 +1053,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.504Z</t>
+    <t>2026-07-25T15:59:36.367Z</t>
   </si>
   <si>
     <t>LOG-SEL-20</t>
@@ -1067,7 +1067,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.538Z</t>
+    <t>2026-07-25T15:59:36.397Z</t>
   </si>
   <si>
     <t>LOG-SEL-21</t>
@@ -1081,7 +1081,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.572Z</t>
+    <t>2026-07-25T15:59:36.428Z</t>
   </si>
   <si>
     <t>LOG-SEL-22</t>
@@ -1095,7 +1095,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.606Z</t>
+    <t>2026-07-25T15:59:36.475Z</t>
   </si>
   <si>
     <t>LOG-SEL-23</t>
@@ -1109,7 +1109,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.649Z</t>
+    <t>2026-07-25T15:59:36.521Z</t>
   </si>
   <si>
     <t>LOG-SEL-24</t>
@@ -1123,7 +1123,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.683Z</t>
+    <t>2026-07-25T15:59:36.551Z</t>
   </si>
   <si>
     <t>LOG-SEL-25</t>
@@ -1137,7 +1137,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.718Z</t>
+    <t>2026-07-25T15:59:36.581Z</t>
   </si>
   <si>
     <t>LOG-SEL-26</t>
@@ -1151,7 +1151,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.760Z</t>
+    <t>2026-07-25T15:59:36.612Z</t>
   </si>
   <si>
     <t>LOG-SEL-27</t>
@@ -1165,7 +1165,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.787Z</t>
+    <t>2026-07-25T15:59:36.658Z</t>
   </si>
   <si>
     <t>LOG-SEL-28</t>
@@ -1179,7 +1179,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.815Z</t>
+    <t>2026-07-25T15:59:36.689Z</t>
   </si>
   <si>
     <t>LOG-SEL-29</t>
@@ -1193,7 +1193,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.843Z</t>
+    <t>2026-07-25T15:59:36.735Z</t>
   </si>
   <si>
     <t>LOG-SEL-30</t>
@@ -1207,7 +1207,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.885Z</t>
+    <t>2026-07-25T15:59:36.766Z</t>
   </si>
   <si>
     <t>LOG-SEL-31</t>
@@ -1221,7 +1221,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.926Z</t>
+    <t>2026-07-25T15:59:36.797Z</t>
   </si>
   <si>
     <t>LOG-SEL-32</t>
@@ -1235,7 +1235,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.961Z</t>
+    <t>2026-07-25T15:59:36.828Z</t>
   </si>
   <si>
     <t>LOG-SEL-33</t>
@@ -1249,7 +1249,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:44.996Z</t>
+    <t>2026-07-25T15:59:36.858Z</t>
   </si>
   <si>
     <t>LOG-SEL-34</t>
@@ -1263,7 +1263,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.037Z</t>
+    <t>2026-07-25T15:59:36.889Z</t>
   </si>
   <si>
     <t>LOG-SEL-35</t>
@@ -1277,7 +1277,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.072Z</t>
+    <t>2026-07-25T15:59:36.920Z</t>
   </si>
   <si>
     <t>LOG-SEL-36</t>
@@ -1291,7 +1291,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.107Z</t>
+    <t>2026-07-25T15:59:36.966Z</t>
   </si>
   <si>
     <t>REG-SEL-01</t>
@@ -1307,7 +1307,7 @@
     <t>Register page renders correctly</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.135Z</t>
+    <t>2026-07-25T15:59:36.997Z</t>
   </si>
   <si>
     <t>REG-SEL-02</t>
@@ -1323,7 +1323,7 @@
     <t>Validation errors shown for all required fields</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.162Z</t>
+    <t>2026-07-25T15:59:37.028Z</t>
   </si>
   <si>
     <t>REG-SEL-03</t>
@@ -1340,7 +1340,7 @@
     <t>Email validation error displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.204Z</t>
+    <t>2026-07-25T15:59:37.076Z</t>
   </si>
   <si>
     <t>REG-SEL-04</t>
@@ -1357,7 +1357,7 @@
     <t>"Passwords do not match" error shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.246Z</t>
+    <t>2026-07-25T15:59:37.107Z</t>
   </si>
   <si>
     <t>REG-SEL-05</t>
@@ -1374,7 +1374,7 @@
     <t>Account created, user redirected to verification or dashboard</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.273Z</t>
+    <t>2026-07-25T15:59:37.139Z</t>
   </si>
   <si>
     <t>REG-SEL-06</t>
@@ -1390,7 +1390,7 @@
     <t>Login page is loaded</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.301Z</t>
+    <t>2026-07-25T15:59:37.184Z</t>
   </si>
   <si>
     <t>REG-SEL-07</t>
@@ -1407,7 +1407,7 @@
     <t>Role selection works in web browser</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.329Z</t>
+    <t>2026-07-25T15:59:37.214Z</t>
   </si>
   <si>
     <t>REG-SEL-08</t>
@@ -1424,7 +1424,7 @@
     <t>Page behaves correctly for Functional capability #8</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.371Z</t>
+    <t>2026-07-25T15:59:37.246Z</t>
   </si>
   <si>
     <t>REG-SEL-09</t>
@@ -1441,7 +1441,7 @@
     <t>Page behaves correctly for Validation capability #9</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.400Z</t>
+    <t>2026-07-25T15:59:37.277Z</t>
   </si>
   <si>
     <t>REG-SEL-10</t>
@@ -1458,7 +1458,7 @@
     <t>Page behaves correctly for Responsive capability #10</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.440Z</t>
+    <t>2026-07-25T15:59:37.308Z</t>
   </si>
   <si>
     <t>REG-SEL-11</t>
@@ -1472,7 +1472,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.484Z</t>
+    <t>2026-07-25T15:59:37.338Z</t>
   </si>
   <si>
     <t>REG-SEL-12</t>
@@ -1486,7 +1486,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.523Z</t>
+    <t>2026-07-25T15:59:37.369Z</t>
   </si>
   <si>
     <t>REG-SEL-13</t>
@@ -1500,7 +1500,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.553Z</t>
+    <t>2026-07-25T15:59:37.400Z</t>
   </si>
   <si>
     <t>REG-SEL-14</t>
@@ -1514,7 +1514,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.600Z</t>
+    <t>2026-07-25T15:59:37.446Z</t>
   </si>
   <si>
     <t>REG-SEL-15</t>
@@ -1528,7 +1528,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.642Z</t>
+    <t>2026-07-25T15:59:37.478Z</t>
   </si>
   <si>
     <t>REG-SEL-16</t>
@@ -1542,7 +1542,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.677Z</t>
+    <t>2026-07-25T15:59:37.508Z</t>
   </si>
   <si>
     <t>REG-SEL-17</t>
@@ -1556,7 +1556,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.718Z</t>
+    <t>2026-07-25T15:59:37.538Z</t>
   </si>
   <si>
     <t>REG-SEL-18</t>
@@ -1570,7 +1570,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.760Z</t>
+    <t>2026-07-25T15:59:37.570Z</t>
   </si>
   <si>
     <t>REG-SEL-19</t>
@@ -1584,7 +1584,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.808Z</t>
+    <t>2026-07-25T15:59:37.600Z</t>
   </si>
   <si>
     <t>REG-SEL-20</t>
@@ -1598,7 +1598,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.852Z</t>
+    <t>2026-07-25T15:59:37.631Z</t>
   </si>
   <si>
     <t>REG-SEL-21</t>
@@ -1612,7 +1612,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.898Z</t>
+    <t>2026-07-25T15:59:37.676Z</t>
   </si>
   <si>
     <t>REG-SEL-22</t>
@@ -1626,7 +1626,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.940Z</t>
+    <t>2026-07-25T15:59:37.707Z</t>
   </si>
   <si>
     <t>REG-SEL-23</t>
@@ -1640,7 +1640,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:45.982Z</t>
+    <t>2026-07-25T15:59:37.738Z</t>
   </si>
   <si>
     <t>REG-SEL-24</t>
@@ -1654,7 +1654,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:46.046Z</t>
+    <t>2026-07-25T15:59:37.784Z</t>
   </si>
   <si>
     <t>REG-SEL-25</t>
@@ -1668,7 +1668,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:46.091Z</t>
+    <t>2026-07-25T15:59:37.830Z</t>
   </si>
   <si>
     <t>REG-SEL-26</t>
@@ -1682,7 +1682,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:46.145Z</t>
+    <t>2026-07-25T15:59:37.863Z</t>
   </si>
   <si>
     <t>REG-SEL-27</t>
@@ -1696,7 +1696,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:46.177Z</t>
+    <t>2026-07-25T15:59:37.894Z</t>
   </si>
   <si>
     <t>REG-SEL-28</t>
@@ -1710,7 +1710,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:46.224Z</t>
+    <t>2026-07-25T15:59:37.941Z</t>
   </si>
   <si>
     <t>REG-SEL-29</t>
@@ -1724,7 +1724,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:46.267Z</t>
+    <t>2026-07-25T15:59:37.987Z</t>
   </si>
   <si>
     <t>REG-SEL-30</t>
@@ -1738,7 +1738,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:46.308Z</t>
+    <t>2026-07-25T15:59:38.018Z</t>
   </si>
   <si>
     <t>REG-SEL-31</t>
@@ -1752,7 +1752,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:46.364Z</t>
+    <t>2026-07-25T15:59:38.065Z</t>
   </si>
   <si>
     <t>REG-SEL-32</t>
@@ -1766,7 +1766,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:46.406Z</t>
+    <t>2026-07-25T15:59:38.111Z</t>
   </si>
   <si>
     <t>REG-SEL-33</t>
@@ -1780,7 +1780,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:46.454Z</t>
+    <t>2026-07-25T15:59:38.141Z</t>
   </si>
   <si>
     <t>REG-SEL-34</t>
@@ -1794,7 +1794,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:46.489Z</t>
+    <t>2026-07-25T15:59:38.172Z</t>
   </si>
   <si>
     <t>REG-SEL-35</t>
@@ -1808,7 +1808,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:46.545Z</t>
+    <t>2026-07-25T15:59:38.218Z</t>
   </si>
   <si>
     <t>REG-SEL-36</t>
@@ -1822,7 +1822,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:46.588Z</t>
+    <t>2026-07-25T15:59:38.266Z</t>
   </si>
   <si>
     <t>FP-SEL-01</t>
@@ -1838,7 +1838,7 @@
     <t>Forgot Password form is rendered</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:46.634Z</t>
+    <t>2026-07-25T15:59:38.296Z</t>
   </si>
   <si>
     <t>FP-SEL-02</t>
@@ -1855,7 +1855,7 @@
     <t>Success message is displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:46.676Z</t>
+    <t>2026-07-25T15:59:38.327Z</t>
   </si>
   <si>
     <t>FP-SEL-03</t>
@@ -1871,7 +1871,7 @@
     <t>Login page is loaded on back navigation</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:46.725Z</t>
+    <t>2026-07-25T15:59:38.374Z</t>
   </si>
   <si>
     <t>FP-SEL-04</t>
@@ -1888,7 +1888,7 @@
     <t>Page behaves correctly for Performance capability #4</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:46.768Z</t>
+    <t>2026-07-25T15:59:38.404Z</t>
   </si>
   <si>
     <t>FP-SEL-05</t>
@@ -1905,7 +1905,7 @@
     <t>Page behaves correctly for Security capability #5</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:46.817Z</t>
+    <t>2026-07-25T15:59:38.450Z</t>
   </si>
   <si>
     <t>FP-SEL-06</t>
@@ -1922,7 +1922,7 @@
     <t>Page behaves correctly for Accessibility capability #6</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:46.864Z</t>
+    <t>2026-07-25T15:59:38.496Z</t>
   </si>
   <si>
     <t>FP-SEL-07</t>
@@ -1939,7 +1939,7 @@
     <t>Page behaves correctly for UI Visibility capability #7</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:46.906Z</t>
+    <t>2026-07-25T15:59:38.541Z</t>
   </si>
   <si>
     <t>FP-SEL-08</t>
@@ -1953,7 +1953,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:46.940Z</t>
+    <t>2026-07-25T15:59:38.571Z</t>
   </si>
   <si>
     <t>FP-SEL-09</t>
@@ -1967,7 +1967,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:46.982Z</t>
+    <t>2026-07-25T15:59:38.602Z</t>
   </si>
   <si>
     <t>FP-SEL-10</t>
@@ -1981,7 +1981,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:47.030Z</t>
+    <t>2026-07-25T15:59:38.633Z</t>
   </si>
   <si>
     <t>FP-SEL-11</t>
@@ -1995,7 +1995,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:47.072Z</t>
+    <t>2026-07-25T15:59:38.679Z</t>
   </si>
   <si>
     <t>FP-SEL-12</t>
@@ -2009,7 +2009,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:47.114Z</t>
+    <t>2026-07-25T15:59:38.709Z</t>
   </si>
   <si>
     <t>FP-SEL-13</t>
@@ -2023,7 +2023,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:47.155Z</t>
+    <t>2026-07-25T15:59:38.740Z</t>
   </si>
   <si>
     <t>FP-SEL-14</t>
@@ -2037,7 +2037,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:47.204Z</t>
+    <t>2026-07-25T15:59:38.771Z</t>
   </si>
   <si>
     <t>FP-SEL-15</t>
@@ -2051,7 +2051,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:47.247Z</t>
+    <t>2026-07-25T15:59:38.817Z</t>
   </si>
   <si>
     <t>FP-SEL-16</t>
@@ -2065,7 +2065,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:47.287Z</t>
+    <t>2026-07-25T15:59:38.863Z</t>
   </si>
   <si>
     <t>FP-SEL-17</t>
@@ -2079,7 +2079,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:47.336Z</t>
+    <t>2026-07-25T15:59:38.910Z</t>
   </si>
   <si>
     <t>FP-SEL-18</t>
@@ -2093,7 +2093,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:47.379Z</t>
+    <t>2026-07-25T15:59:38.940Z</t>
   </si>
   <si>
     <t>FP-SEL-19</t>
@@ -2107,7 +2107,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:47.419Z</t>
+    <t>2026-07-25T15:59:38.986Z</t>
   </si>
   <si>
     <t>FP-SEL-20</t>
@@ -2121,7 +2121,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:47.461Z</t>
+    <t>2026-07-25T15:59:39.032Z</t>
   </si>
   <si>
     <t>FP-SEL-21</t>
@@ -2135,7 +2135,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:47.510Z</t>
+    <t>2026-07-25T15:59:39.062Z</t>
   </si>
   <si>
     <t>FP-SEL-22</t>
@@ -2149,7 +2149,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:47.551Z</t>
+    <t>2026-07-25T15:59:39.093Z</t>
   </si>
   <si>
     <t>FP-SEL-23</t>
@@ -2163,7 +2163,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:47.600Z</t>
+    <t>2026-07-25T15:59:39.124Z</t>
   </si>
   <si>
     <t>FP-SEL-24</t>
@@ -2177,7 +2177,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:47.649Z</t>
+    <t>2026-07-25T15:59:39.170Z</t>
   </si>
   <si>
     <t>FP-SEL-25</t>
@@ -2191,7 +2191,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:47.686Z</t>
+    <t>2026-07-25T15:59:39.216Z</t>
   </si>
   <si>
     <t>FP-SEL-26</t>
@@ -2205,7 +2205,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:47.727Z</t>
+    <t>2026-07-25T15:59:39.262Z</t>
   </si>
   <si>
     <t>FP-SEL-27</t>
@@ -2219,7 +2219,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:47.788Z</t>
+    <t>2026-07-25T15:59:39.309Z</t>
   </si>
   <si>
     <t>FP-SEL-28</t>
@@ -2233,7 +2233,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:47.836Z</t>
+    <t>2026-07-25T15:59:39.341Z</t>
   </si>
   <si>
     <t>FP-SEL-29</t>
@@ -2247,7 +2247,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:47.899Z</t>
+    <t>2026-07-25T15:59:39.371Z</t>
   </si>
   <si>
     <t>FP-SEL-30</t>
@@ -2261,7 +2261,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:47.947Z</t>
+    <t>2026-07-25T15:59:39.402Z</t>
   </si>
   <si>
     <t>FP-SEL-31</t>
@@ -2275,7 +2275,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:47.989Z</t>
+    <t>2026-07-25T15:59:39.432Z</t>
   </si>
   <si>
     <t>FP-SEL-32</t>
@@ -2289,7 +2289,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:48.041Z</t>
+    <t>2026-07-25T15:59:39.479Z</t>
   </si>
   <si>
     <t>FP-SEL-33</t>
@@ -2303,7 +2303,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:48.087Z</t>
+    <t>2026-07-25T15:59:39.510Z</t>
   </si>
   <si>
     <t>FP-SEL-34</t>
@@ -2317,7 +2317,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:48.130Z</t>
+    <t>2026-07-25T15:59:39.556Z</t>
   </si>
   <si>
     <t>FP-SEL-35</t>
@@ -2331,7 +2331,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:48.170Z</t>
+    <t>2026-07-25T15:59:39.586Z</t>
   </si>
   <si>
     <t>FP-SEL-36</t>
@@ -2345,7 +2345,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:48.220Z</t>
+    <t>2026-07-25T15:59:39.634Z</t>
   </si>
   <si>
     <t>DASH-SEL-01</t>
@@ -2362,7 +2362,7 @@
     <t>Dashboard page is loaded and URL is /dashboard</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:48.267Z</t>
+    <t>2026-07-25T15:59:39.680Z</t>
   </si>
   <si>
     <t>Mocked. Target: https://tamilarasan13092005.github.io/volunteersync/</t>
@@ -2381,7 +2381,7 @@
     <t>"Dashboard Overview" text is rendered in DOM</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:48.305Z</t>
+    <t>2026-07-25T15:59:39.709Z</t>
   </si>
   <si>
     <t>DASH-SEL-03</t>
@@ -2396,7 +2396,7 @@
     <t>Total Volunteers card is visible</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:48.350Z</t>
+    <t>2026-07-25T15:59:39.741Z</t>
   </si>
   <si>
     <t>DASH-SEL-04</t>
@@ -2411,7 +2411,7 @@
     <t>Active Events card is visible</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:48.392Z</t>
+    <t>2026-07-25T15:59:39.786Z</t>
   </si>
   <si>
     <t>DASH-SEL-05</t>
@@ -2426,7 +2426,7 @@
     <t>Hours This Month card is visible</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:48.433Z</t>
+    <t>2026-07-25T15:59:39.833Z</t>
   </si>
   <si>
     <t>DASH-SEL-06</t>
@@ -2441,7 +2441,7 @@
     <t>Attendance Rate card is visible</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:48.483Z</t>
+    <t>2026-07-25T15:59:39.864Z</t>
   </si>
   <si>
     <t>DASH-SEL-07</t>
@@ -2457,7 +2457,7 @@
     <t>AI Insights banner renders with text content</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:48.530Z</t>
+    <t>2026-07-25T15:59:39.910Z</t>
   </si>
   <si>
     <t>DASH-SEL-08</t>
@@ -2473,7 +2473,7 @@
     <t>AI Chat route is loaded</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:48.586Z</t>
+    <t>2026-07-25T15:59:39.972Z</t>
   </si>
   <si>
     <t>DASH-SEL-09</t>
@@ -2488,7 +2488,7 @@
     <t>Growth chart canvas element is in DOM</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:48.642Z</t>
+    <t>2026-07-25T15:59:40.003Z</t>
   </si>
   <si>
     <t>DASH-SEL-10</t>
@@ -2503,7 +2503,7 @@
     <t>Category chart canvas is in DOM</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:48.690Z</t>
+    <t>2026-07-25T15:59:40.034Z</t>
   </si>
   <si>
     <t>DASH-SEL-11</t>
@@ -2518,7 +2518,7 @@
     <t>Attendance chart canvas is in DOM</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:48.760Z</t>
+    <t>2026-07-25T15:59:40.079Z</t>
   </si>
   <si>
     <t>DASH-SEL-12</t>
@@ -2534,7 +2534,7 @@
     <t>Activity feed renders with items</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:48.815Z</t>
+    <t>2026-07-25T15:59:40.126Z</t>
   </si>
   <si>
     <t>DASH-SEL-13</t>
@@ -2550,7 +2550,7 @@
     <t>Volunteers route is loaded</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:48.871Z</t>
+    <t>2026-07-25T15:59:40.172Z</t>
   </si>
   <si>
     <t>DASH-SEL-14</t>
@@ -2566,7 +2566,7 @@
     <t>Events route is loaded</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:48.927Z</t>
+    <t>2026-07-25T15:59:40.218Z</t>
   </si>
   <si>
     <t>DASH-SEL-15</t>
@@ -2582,7 +2582,7 @@
     <t>Attendance route is loaded</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:48.979Z</t>
+    <t>2026-07-25T15:59:40.264Z</t>
   </si>
   <si>
     <t>DASH-SEL-16</t>
@@ -2598,7 +2598,7 @@
     <t>Reports route is loaded</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:49.030Z</t>
+    <t>2026-07-25T15:59:40.310Z</t>
   </si>
   <si>
     <t>DASH-SEL-17</t>
@@ -2614,7 +2614,7 @@
     <t>Settings route is loaded</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:49.087Z</t>
+    <t>2026-07-25T15:59:40.356Z</t>
   </si>
   <si>
     <t>DASH-SEL-18</t>
@@ -2631,7 +2631,7 @@
     <t>Dashboard adapts to 1280x800 without overflow</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:49.128Z</t>
+    <t>2026-07-25T15:59:40.403Z</t>
   </si>
   <si>
     <t>DASH-SEL-19</t>
@@ -2647,7 +2647,7 @@
     <t>Dashboard uses mobile grid layout at 375px width</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:49.183Z</t>
+    <t>2026-07-25T15:59:40.434Z</t>
   </si>
   <si>
     <t>DASH-SEL-20</t>
@@ -2664,7 +2664,7 @@
     <t>Dashboard is interactive within 10 seconds</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:49.239Z</t>
+    <t>2026-07-25T15:59:40.480Z</t>
   </si>
   <si>
     <t>DASH-SEL-21</t>
@@ -2678,7 +2678,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:49.294Z</t>
+    <t>2026-07-25T15:59:40.528Z</t>
   </si>
   <si>
     <t>DASH-SEL-22</t>
@@ -2692,7 +2692,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:49.350Z</t>
+    <t>2026-07-25T15:59:40.573Z</t>
   </si>
   <si>
     <t>DASH-SEL-23</t>
@@ -2706,7 +2706,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:49.413Z</t>
+    <t>2026-07-25T15:59:40.619Z</t>
   </si>
   <si>
     <t>DASH-SEL-24</t>
@@ -2720,7 +2720,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:49.455Z</t>
+    <t>2026-07-25T15:59:40.665Z</t>
   </si>
   <si>
     <t>DASH-SEL-25</t>
@@ -2734,7 +2734,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:49.510Z</t>
+    <t>2026-07-25T15:59:40.696Z</t>
   </si>
   <si>
     <t>DASH-SEL-26</t>
@@ -2748,7 +2748,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:49.558Z</t>
+    <t>2026-07-25T15:59:40.758Z</t>
   </si>
   <si>
     <t>DASH-SEL-27</t>
@@ -2762,7 +2762,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:49.614Z</t>
+    <t>2026-07-25T15:59:40.803Z</t>
   </si>
   <si>
     <t>DASH-SEL-28</t>
@@ -2776,7 +2776,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:49.657Z</t>
+    <t>2026-07-25T15:59:40.849Z</t>
   </si>
   <si>
     <t>DASH-SEL-29</t>
@@ -2790,7 +2790,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:49.704Z</t>
+    <t>2026-07-25T15:59:40.896Z</t>
   </si>
   <si>
     <t>DASH-SEL-30</t>
@@ -2804,7 +2804,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:49.760Z</t>
+    <t>2026-07-25T15:59:40.942Z</t>
   </si>
   <si>
     <t>DASH-SEL-31</t>
@@ -2818,7 +2818,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:49.815Z</t>
+    <t>2026-07-25T15:59:40.988Z</t>
   </si>
   <si>
     <t>DASH-SEL-32</t>
@@ -2832,7 +2832,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:49.857Z</t>
+    <t>2026-07-25T15:59:41.034Z</t>
   </si>
   <si>
     <t>DASH-SEL-33</t>
@@ -2846,7 +2846,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:49.912Z</t>
+    <t>2026-07-25T15:59:41.080Z</t>
   </si>
   <si>
     <t>DASH-SEL-34</t>
@@ -2860,7 +2860,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:49.954Z</t>
+    <t>2026-07-25T15:59:41.127Z</t>
   </si>
   <si>
     <t>DASH-SEL-35</t>
@@ -2874,7 +2874,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:50.009Z</t>
+    <t>2026-07-25T15:59:41.173Z</t>
   </si>
   <si>
     <t>DASH-SEL-36</t>
@@ -2888,7 +2888,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:50.065Z</t>
+    <t>2026-07-25T15:59:41.219Z</t>
   </si>
   <si>
     <t>VOL-SEL-01</t>
@@ -2904,7 +2904,7 @@
     <t>Volunteers page renders</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:50.121Z</t>
+    <t>2026-07-25T15:59:41.281Z</t>
   </si>
   <si>
     <t>VOL-SEL-02</t>
@@ -2920,7 +2920,7 @@
     <t>Volunteer cards are rendered</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:50.173Z</t>
+    <t>2026-07-25T15:59:41.326Z</t>
   </si>
   <si>
     <t>VOL-SEL-03</t>
@@ -2936,7 +2936,7 @@
     <t>List filters to matching names</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:50.239Z</t>
+    <t>2026-07-25T15:59:41.373Z</t>
   </si>
   <si>
     <t>VOL-SEL-04</t>
@@ -2952,7 +2952,7 @@
     <t>Only active volunteers displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:50.301Z</t>
+    <t>2026-07-25T15:59:41.420Z</t>
   </si>
   <si>
     <t>VOL-SEL-05</t>
@@ -2968,7 +2968,7 @@
     <t>Add Volunteer dialog opens</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:50.357Z</t>
+    <t>2026-07-25T15:59:41.467Z</t>
   </si>
   <si>
     <t>VOL-SEL-06</t>
@@ -2985,7 +2985,7 @@
     <t>Validation errors shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:50.409Z</t>
+    <t>2026-07-25T15:59:41.513Z</t>
   </si>
   <si>
     <t>VOL-SEL-07</t>
@@ -3002,7 +3002,7 @@
     <t>New volunteer appears in list</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:50.461Z</t>
+    <t>2026-07-25T15:59:41.559Z</t>
   </si>
   <si>
     <t>VOL-SEL-08</t>
@@ -3018,7 +3018,7 @@
     <t>Volunteer detail is shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:50.516Z</t>
+    <t>2026-07-25T15:59:41.607Z</t>
   </si>
   <si>
     <t>VOL-SEL-09</t>
@@ -3034,7 +3034,7 @@
     <t>Avatar, name, role visible on each card</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:50.579Z</t>
+    <t>2026-07-25T15:59:41.654Z</t>
   </si>
   <si>
     <t>VOL-SEL-10</t>
@@ -3050,7 +3050,7 @@
     <t>Mobile layout renders correctly</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:50.665Z</t>
+    <t>2026-07-25T15:59:41.700Z</t>
   </si>
   <si>
     <t>VOL-SEL-11</t>
@@ -3066,7 +3066,7 @@
     <t>"No volunteers found" shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:50.711Z</t>
+    <t>2026-07-25T15:59:41.747Z</t>
   </si>
   <si>
     <t>VOL-SEL-12</t>
@@ -3081,7 +3081,7 @@
     <t>Button is accessible with descriptive label</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:50.758Z</t>
+    <t>2026-07-25T15:59:41.793Z</t>
   </si>
   <si>
     <t>VOL-SEL-13</t>
@@ -3095,7 +3095,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:50.803Z</t>
+    <t>2026-07-25T15:59:41.839Z</t>
   </si>
   <si>
     <t>VOL-SEL-14</t>
@@ -3109,7 +3109,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:50.851Z</t>
+    <t>2026-07-25T15:59:41.886Z</t>
   </si>
   <si>
     <t>VOL-SEL-15</t>
@@ -3123,7 +3123,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:50.906Z</t>
+    <t>2026-07-25T15:59:41.931Z</t>
   </si>
   <si>
     <t>VOL-SEL-16</t>
@@ -3137,7 +3137,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:50.961Z</t>
+    <t>2026-07-25T15:59:41.978Z</t>
   </si>
   <si>
     <t>VOL-SEL-17</t>
@@ -3151,7 +3151,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:51.017Z</t>
+    <t>2026-07-25T15:59:42.025Z</t>
   </si>
   <si>
     <t>VOL-SEL-18</t>
@@ -3165,7 +3165,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:51.076Z</t>
+    <t>2026-07-25T15:59:42.071Z</t>
   </si>
   <si>
     <t>VOL-SEL-19</t>
@@ -3179,7 +3179,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:51.155Z</t>
+    <t>2026-07-25T15:59:42.116Z</t>
   </si>
   <si>
     <t>VOL-SEL-20</t>
@@ -3193,7 +3193,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:51.197Z</t>
+    <t>2026-07-25T15:59:42.164Z</t>
   </si>
   <si>
     <t>VOL-SEL-21</t>
@@ -3207,7 +3207,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:51.260Z</t>
+    <t>2026-07-25T15:59:42.211Z</t>
   </si>
   <si>
     <t>VOL-SEL-22</t>
@@ -3221,7 +3221,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:51.315Z</t>
+    <t>2026-07-25T15:59:42.256Z</t>
   </si>
   <si>
     <t>VOL-SEL-23</t>
@@ -3235,7 +3235,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:51.371Z</t>
+    <t>2026-07-25T15:59:42.302Z</t>
   </si>
   <si>
     <t>VOL-SEL-24</t>
@@ -3249,7 +3249,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:51.433Z</t>
+    <t>2026-07-25T15:59:42.348Z</t>
   </si>
   <si>
     <t>VOL-SEL-25</t>
@@ -3263,7 +3263,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:51.488Z</t>
+    <t>2026-07-25T15:59:42.395Z</t>
   </si>
   <si>
     <t>VOL-SEL-26</t>
@@ -3277,7 +3277,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:51.552Z</t>
+    <t>2026-07-25T15:59:42.442Z</t>
   </si>
   <si>
     <t>VOL-SEL-27</t>
@@ -3291,7 +3291,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:51.621Z</t>
+    <t>2026-07-25T15:59:42.488Z</t>
   </si>
   <si>
     <t>VOL-SEL-28</t>
@@ -3305,7 +3305,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:51.683Z</t>
+    <t>2026-07-25T15:59:42.534Z</t>
   </si>
   <si>
     <t>VOL-SEL-29</t>
@@ -3319,7 +3319,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:51.753Z</t>
+    <t>2026-07-25T15:59:42.579Z</t>
   </si>
   <si>
     <t>VOL-SEL-30</t>
@@ -3333,7 +3333,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:51.816Z</t>
+    <t>2026-07-25T15:59:42.626Z</t>
   </si>
   <si>
     <t>VOL-SEL-31</t>
@@ -3347,7 +3347,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:51.871Z</t>
+    <t>2026-07-25T15:59:42.687Z</t>
   </si>
   <si>
     <t>VOL-SEL-32</t>
@@ -3361,7 +3361,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:51.933Z</t>
+    <t>2026-07-25T15:59:42.734Z</t>
   </si>
   <si>
     <t>VOL-SEL-33</t>
@@ -3375,7 +3375,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:51.996Z</t>
+    <t>2026-07-25T15:59:42.780Z</t>
   </si>
   <si>
     <t>VOL-SEL-34</t>
@@ -3389,7 +3389,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:52.051Z</t>
+    <t>2026-07-25T15:59:42.843Z</t>
   </si>
   <si>
     <t>VOL-SEL-35</t>
@@ -3403,7 +3403,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:52.122Z</t>
+    <t>2026-07-25T15:59:42.890Z</t>
   </si>
   <si>
     <t>VOL-SEL-36</t>
@@ -3417,7 +3417,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:52.171Z</t>
+    <t>2026-07-25T15:59:42.952Z</t>
   </si>
   <si>
     <t>VOL-SEL-37</t>
@@ -3434,7 +3434,7 @@
     <t>Page behaves correctly for Validation capability #37</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:52.226Z</t>
+    <t>2026-07-25T15:59:42.998Z</t>
   </si>
   <si>
     <t>EVT-SEL-01</t>
@@ -3450,7 +3450,7 @@
     <t>Events page renders with title</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:52.280Z</t>
+    <t>2026-07-25T15:59:43.044Z</t>
   </si>
   <si>
     <t>EVT-SEL-02</t>
@@ -3466,7 +3466,7 @@
     <t>Event cards render with info</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:52.336Z</t>
+    <t>2026-07-25T15:59:43.091Z</t>
   </si>
   <si>
     <t>EVT-SEL-03</t>
@@ -3482,7 +3482,7 @@
     <t>Events filter by search query</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:52.406Z</t>
+    <t>2026-07-25T15:59:43.137Z</t>
   </si>
   <si>
     <t>EVT-SEL-04</t>
@@ -3498,7 +3498,7 @@
     <t>Only upcoming events displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:52.468Z</t>
+    <t>2026-07-25T15:59:43.183Z</t>
   </si>
   <si>
     <t>EVT-SEL-05</t>
@@ -3514,7 +3514,7 @@
     <t>Only completed events displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:52.544Z</t>
+    <t>2026-07-25T15:59:43.230Z</t>
   </si>
   <si>
     <t>EVT-SEL-06</t>
@@ -3530,7 +3530,7 @@
     <t>Create Event dialog opens</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:52.600Z</t>
+    <t>2026-07-25T15:59:43.277Z</t>
   </si>
   <si>
     <t>EVT-SEL-07</t>
@@ -3547,7 +3547,7 @@
     <t>Validation errors for required fields</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:52.663Z</t>
+    <t>2026-07-25T15:59:43.323Z</t>
   </si>
   <si>
     <t>EVT-SEL-08</t>
@@ -3564,7 +3564,7 @@
     <t>"Event created successfully!" shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:52.712Z</t>
+    <t>2026-07-25T15:59:43.369Z</t>
   </si>
   <si>
     <t>EVT-SEL-09</t>
@@ -3581,7 +3581,7 @@
     <t>All 6 event categories are selectable</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:52.767Z</t>
+    <t>2026-07-25T15:59:43.416Z</t>
   </si>
   <si>
     <t>EVT-SEL-10</t>
@@ -3597,7 +3597,7 @@
     <t>Event detail is displayed on click</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:52.836Z</t>
+    <t>2026-07-25T15:59:43.463Z</t>
   </si>
   <si>
     <t>EVT-SEL-11</t>
@@ -3613,7 +3613,7 @@
     <t>All event metadata fields visible</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:52.895Z</t>
+    <t>2026-07-25T15:59:43.509Z</t>
   </si>
   <si>
     <t>EVT-SEL-12</t>
@@ -3628,7 +3628,7 @@
     <t>Fill rate progress bar is visible</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:52.964Z</t>
+    <t>2026-07-25T15:59:43.554Z</t>
   </si>
   <si>
     <t>EVT-SEL-13</t>
@@ -3644,7 +3644,7 @@
     <t>Events renders correctly at 768px</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:53.024Z</t>
+    <t>2026-07-25T15:59:43.600Z</t>
   </si>
   <si>
     <t>EVT-SEL-14</t>
@@ -3662,7 +3662,7 @@
     <t>Dialog closes without creating event</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:53.086Z</t>
+    <t>2026-07-25T15:59:43.646Z</t>
   </si>
   <si>
     <t>EVT-SEL-15</t>
@@ -3677,7 +3677,7 @@
     <t>Status badge colors are correct</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:53.141Z</t>
+    <t>2026-07-25T15:59:43.691Z</t>
   </si>
   <si>
     <t>EVT-SEL-16</t>
@@ -3691,7 +3691,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:53.210Z</t>
+    <t>2026-07-25T15:59:43.753Z</t>
   </si>
   <si>
     <t>EVT-SEL-17</t>
@@ -3705,7 +3705,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:53.285Z</t>
+    <t>2026-07-25T15:59:43.799Z</t>
   </si>
   <si>
     <t>EVT-SEL-18</t>
@@ -3719,7 +3719,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:53.373Z</t>
+    <t>2026-07-25T15:59:43.846Z</t>
   </si>
   <si>
     <t>EVT-SEL-19</t>
@@ -3733,7 +3733,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:53.459Z</t>
+    <t>2026-07-25T15:59:43.907Z</t>
   </si>
   <si>
     <t>EVT-SEL-20</t>
@@ -3747,7 +3747,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:53.542Z</t>
+    <t>2026-07-25T15:59:43.954Z</t>
   </si>
   <si>
     <t>EVT-SEL-21</t>
@@ -3761,7 +3761,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:53.637Z</t>
+    <t>2026-07-25T15:59:44.016Z</t>
   </si>
   <si>
     <t>EVT-SEL-22</t>
@@ -3775,7 +3775,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:53.725Z</t>
+    <t>2026-07-25T15:59:44.061Z</t>
   </si>
   <si>
     <t>EVT-SEL-23</t>
@@ -3789,7 +3789,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:53.810Z</t>
+    <t>2026-07-25T15:59:44.106Z</t>
   </si>
   <si>
     <t>EVT-SEL-24</t>
@@ -3803,7 +3803,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:53.878Z</t>
+    <t>2026-07-25T15:59:44.153Z</t>
   </si>
   <si>
     <t>EVT-SEL-25</t>
@@ -3817,7 +3817,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:53.972Z</t>
+    <t>2026-07-25T15:59:44.199Z</t>
   </si>
   <si>
     <t>EVT-SEL-26</t>
@@ -3831,7 +3831,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:54.065Z</t>
+    <t>2026-07-25T15:59:44.246Z</t>
   </si>
   <si>
     <t>EVT-SEL-27</t>
@@ -3845,7 +3845,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:54.149Z</t>
+    <t>2026-07-25T15:59:44.292Z</t>
   </si>
   <si>
     <t>EVT-SEL-28</t>
@@ -3859,7 +3859,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:54.236Z</t>
+    <t>2026-07-25T15:59:44.338Z</t>
   </si>
   <si>
     <t>EVT-SEL-29</t>
@@ -3873,7 +3873,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:54.304Z</t>
+    <t>2026-07-25T15:59:44.384Z</t>
   </si>
   <si>
     <t>EVT-SEL-30</t>
@@ -3887,7 +3887,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:54.383Z</t>
+    <t>2026-07-25T15:59:44.445Z</t>
   </si>
   <si>
     <t>EVT-SEL-31</t>
@@ -3901,7 +3901,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:54.475Z</t>
+    <t>2026-07-25T15:59:44.491Z</t>
   </si>
   <si>
     <t>EVT-SEL-32</t>
@@ -3915,7 +3915,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:54.558Z</t>
+    <t>2026-07-25T15:59:44.537Z</t>
   </si>
   <si>
     <t>EVT-SEL-33</t>
@@ -3929,7 +3929,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:54.645Z</t>
+    <t>2026-07-25T15:59:44.583Z</t>
   </si>
   <si>
     <t>EVT-SEL-34</t>
@@ -3943,7 +3943,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:54.718Z</t>
+    <t>2026-07-25T15:59:44.629Z</t>
   </si>
   <si>
     <t>EVT-SEL-35</t>
@@ -3957,7 +3957,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:54.817Z</t>
+    <t>2026-07-25T15:59:44.676Z</t>
   </si>
   <si>
     <t>EVT-SEL-36</t>
@@ -3971,7 +3971,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:54.898Z</t>
+    <t>2026-07-25T15:59:44.737Z</t>
   </si>
   <si>
     <t>EVT-SEL-37</t>
@@ -3985,7 +3985,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:54.968Z</t>
+    <t>2026-07-25T15:59:44.784Z</t>
   </si>
   <si>
     <t>ATT-SEL-01</t>
@@ -4001,7 +4001,7 @@
     <t>Attendance page renders</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:55.052Z</t>
+    <t>2026-07-25T15:59:44.831Z</t>
   </si>
   <si>
     <t>ATT-SEL-02</t>
@@ -4016,7 +4016,7 @@
     <t>All 4 summary chips are visible</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:55.135Z</t>
+    <t>2026-07-25T15:59:44.877Z</t>
   </si>
   <si>
     <t>ATT-SEL-03</t>
@@ -4032,7 +4032,7 @@
     <t>Tab switch works correctly</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:55.220Z</t>
+    <t>2026-07-25T15:59:44.924Z</t>
   </si>
   <si>
     <t>ATT-SEL-04</t>
@@ -4047,7 +4047,7 @@
     <t>Records are displayed in list</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:55.307Z</t>
+    <t>2026-07-25T15:59:44.985Z</t>
   </si>
   <si>
     <t>ATT-SEL-05</t>
@@ -4063,7 +4063,7 @@
     <t>Records filtered by volunteer name</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:55.388Z</t>
+    <t>2026-07-25T15:59:45.031Z</t>
   </si>
   <si>
     <t>ATT-SEL-06</t>
@@ -4079,7 +4079,7 @@
     <t>Only present records shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:55.482Z</t>
+    <t>2026-07-25T15:59:45.077Z</t>
   </si>
   <si>
     <t>ATT-SEL-07</t>
@@ -4095,7 +4095,7 @@
     <t>Check-in dialog is displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:55.571Z</t>
+    <t>2026-07-25T15:59:45.123Z</t>
   </si>
   <si>
     <t>ATT-SEL-08</t>
@@ -4113,7 +4113,7 @@
     <t>Success snackbar is shown</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:55.690Z</t>
+    <t>2026-07-25T15:59:45.186Z</t>
   </si>
   <si>
     <t>ATT-SEL-09</t>
@@ -4131,7 +4131,7 @@
     <t>Empty name prevents check-in</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:55.745Z</t>
+    <t>2026-07-25T15:59:45.247Z</t>
   </si>
   <si>
     <t>ATT-SEL-10</t>
@@ -4147,7 +4147,7 @@
     <t>By Event tab shows events with progress</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:55.816Z</t>
+    <t>2026-07-25T15:59:45.308Z</t>
   </si>
   <si>
     <t>ATT-SEL-11</t>
@@ -4164,7 +4164,7 @@
     <t>All events listed in dropdown</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:55.884Z</t>
+    <t>2026-07-25T15:59:45.356Z</t>
   </si>
   <si>
     <t>ATT-SEL-12</t>
@@ -4177,7 +4177,7 @@
 2. Assert layout adapts without overflow</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:55.963Z</t>
+    <t>2026-07-25T15:59:45.403Z</t>
   </si>
   <si>
     <t>ATT-SEL-13</t>
@@ -4191,7 +4191,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:56.035Z</t>
+    <t>2026-07-25T15:59:45.465Z</t>
   </si>
   <si>
     <t>ATT-SEL-14</t>
@@ -4205,7 +4205,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:56.167Z</t>
+    <t>2026-07-25T15:59:45.527Z</t>
   </si>
   <si>
     <t>ATT-SEL-15</t>
@@ -4219,7 +4219,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:56.224Z</t>
+    <t>2026-07-25T15:59:45.574Z</t>
   </si>
   <si>
     <t>ATT-SEL-16</t>
@@ -4233,7 +4233,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:56.287Z</t>
+    <t>2026-07-25T15:59:45.637Z</t>
   </si>
   <si>
     <t>ATT-SEL-17</t>
@@ -4247,7 +4247,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:56.359Z</t>
+    <t>2026-07-25T15:59:45.684Z</t>
   </si>
   <si>
     <t>ATT-SEL-18</t>
@@ -4261,7 +4261,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:56.439Z</t>
+    <t>2026-07-25T15:59:45.747Z</t>
   </si>
   <si>
     <t>ATT-SEL-19</t>
@@ -4275,7 +4275,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:56.537Z</t>
+    <t>2026-07-25T15:59:45.794Z</t>
   </si>
   <si>
     <t>ATT-SEL-20</t>
@@ -4289,7 +4289,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:56.634Z</t>
+    <t>2026-07-25T15:59:45.856Z</t>
   </si>
   <si>
     <t>ATT-SEL-21</t>
@@ -4303,7 +4303,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:56.722Z</t>
+    <t>2026-07-25T15:59:45.918Z</t>
   </si>
   <si>
     <t>ATT-SEL-22</t>
@@ -4317,7 +4317,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:56.817Z</t>
+    <t>2026-07-25T15:59:45.964Z</t>
   </si>
   <si>
     <t>ATT-SEL-23</t>
@@ -4331,7 +4331,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:56.907Z</t>
+    <t>2026-07-25T15:59:46.026Z</t>
   </si>
   <si>
     <t>ATT-SEL-24</t>
@@ -4345,7 +4345,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:57.002Z</t>
+    <t>2026-07-25T15:59:46.087Z</t>
   </si>
   <si>
     <t>ATT-SEL-25</t>
@@ -4359,7 +4359,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:57.100Z</t>
+    <t>2026-07-25T15:59:46.149Z</t>
   </si>
   <si>
     <t>ATT-SEL-26</t>
@@ -4373,7 +4373,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:57.204Z</t>
+    <t>2026-07-25T15:59:46.211Z</t>
   </si>
   <si>
     <t>ATT-SEL-27</t>
@@ -4387,7 +4387,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:57.299Z</t>
+    <t>2026-07-25T15:59:46.273Z</t>
   </si>
   <si>
     <t>ATT-SEL-28</t>
@@ -4401,7 +4401,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:57.370Z</t>
+    <t>2026-07-25T15:59:46.335Z</t>
   </si>
   <si>
     <t>ATT-SEL-29</t>
@@ -4415,7 +4415,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:57.461Z</t>
+    <t>2026-07-25T15:59:46.383Z</t>
   </si>
   <si>
     <t>ATT-SEL-30</t>
@@ -4429,7 +4429,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:57.555Z</t>
+    <t>2026-07-25T15:59:46.430Z</t>
   </si>
   <si>
     <t>ATT-SEL-31</t>
@@ -4443,7 +4443,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:57.635Z</t>
+    <t>2026-07-25T15:59:46.490Z</t>
   </si>
   <si>
     <t>ATT-SEL-32</t>
@@ -4457,7 +4457,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:57.715Z</t>
+    <t>2026-07-25T15:59:46.552Z</t>
   </si>
   <si>
     <t>ATT-SEL-33</t>
@@ -4471,7 +4471,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:57.818Z</t>
+    <t>2026-07-25T15:59:46.614Z</t>
   </si>
   <si>
     <t>ATT-SEL-34</t>
@@ -4485,7 +4485,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:57.901Z</t>
+    <t>2026-07-25T15:59:46.676Z</t>
   </si>
   <si>
     <t>ATT-SEL-35</t>
@@ -4499,7 +4499,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:57.977Z</t>
+    <t>2026-07-25T15:59:46.738Z</t>
   </si>
   <si>
     <t>ATT-SEL-36</t>
@@ -4513,7 +4513,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:58.043Z</t>
+    <t>2026-07-25T15:59:46.800Z</t>
   </si>
   <si>
     <t>ATT-SEL-37</t>
@@ -4527,7 +4527,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:58.134Z</t>
+    <t>2026-07-25T15:59:46.862Z</t>
   </si>
   <si>
     <t>REP-SEL-01</t>
@@ -4543,7 +4543,7 @@
     <t>Reports page renders</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:58.201Z</t>
+    <t>2026-07-25T15:59:46.924Z</t>
   </si>
   <si>
     <t>REP-SEL-02</t>
@@ -4558,7 +4558,7 @@
     <t>All KPI cards visible</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:58.282Z</t>
+    <t>2026-07-25T15:59:46.986Z</t>
   </si>
   <si>
     <t>REP-SEL-03</t>
@@ -4573,7 +4573,7 @@
     <t>Chart canvases are in DOM</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:58.345Z</t>
+    <t>2026-07-25T15:59:47.032Z</t>
   </si>
   <si>
     <t>REP-SEL-04</t>
@@ -4589,7 +4589,7 @@
     <t>Report data updates on filter change</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:58.426Z</t>
+    <t>2026-07-25T15:59:47.094Z</t>
   </si>
   <si>
     <t>REP-SEL-05</t>
@@ -4605,7 +4605,7 @@
     <t>Export is triggered</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:58.506Z</t>
+    <t>2026-07-25T15:59:47.156Z</t>
   </si>
   <si>
     <t>REP-SEL-06</t>
@@ -4621,7 +4621,7 @@
     <t>Leaderboard renders with data</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:58.578Z</t>
+    <t>2026-07-25T15:59:47.217Z</t>
   </si>
   <si>
     <t>REP-SEL-07</t>
@@ -4637,7 +4637,7 @@
     <t>Reports layout is mobile-friendly</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:58.665Z</t>
+    <t>2026-07-25T15:59:47.279Z</t>
   </si>
   <si>
     <t>REP-SEL-08</t>
@@ -4653,7 +4653,7 @@
     <t>Page loads in under 10 seconds</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:58.729Z</t>
+    <t>2026-07-25T15:59:47.341Z</t>
   </si>
   <si>
     <t>REP-SEL-09</t>
@@ -4667,7 +4667,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:58.808Z</t>
+    <t>2026-07-25T15:59:47.403Z</t>
   </si>
   <si>
     <t>REP-SEL-10</t>
@@ -4681,7 +4681,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:58.925Z</t>
+    <t>2026-07-25T15:59:47.496Z</t>
   </si>
   <si>
     <t>REP-SEL-11</t>
@@ -4695,7 +4695,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:59.027Z</t>
+    <t>2026-07-25T15:59:47.558Z</t>
   </si>
   <si>
     <t>REP-SEL-12</t>
@@ -4709,7 +4709,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:59.122Z</t>
+    <t>2026-07-25T15:59:47.621Z</t>
   </si>
   <si>
     <t>REP-SEL-13</t>
@@ -4723,7 +4723,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:59.210Z</t>
+    <t>2026-07-25T15:59:47.681Z</t>
   </si>
   <si>
     <t>REP-SEL-14</t>
@@ -4737,7 +4737,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:59.304Z</t>
+    <t>2026-07-25T15:59:47.744Z</t>
   </si>
   <si>
     <t>REP-SEL-15</t>
@@ -4751,7 +4751,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:59.397Z</t>
+    <t>2026-07-25T15:59:47.806Z</t>
   </si>
   <si>
     <t>REP-SEL-16</t>
@@ -4765,7 +4765,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:59.468Z</t>
+    <t>2026-07-25T15:59:47.868Z</t>
   </si>
   <si>
     <t>REP-SEL-17</t>
@@ -4779,7 +4779,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:59.540Z</t>
+    <t>2026-07-25T15:59:47.929Z</t>
   </si>
   <si>
     <t>REP-SEL-18</t>
@@ -4793,7 +4793,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:59.611Z</t>
+    <t>2026-07-25T15:59:48.005Z</t>
   </si>
   <si>
     <t>REP-SEL-19</t>
@@ -4807,7 +4807,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:59.692Z</t>
+    <t>2026-07-25T15:59:48.066Z</t>
   </si>
   <si>
     <t>REP-SEL-20</t>
@@ -4821,7 +4821,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:59.763Z</t>
+    <t>2026-07-25T15:59:48.128Z</t>
   </si>
   <si>
     <t>REP-SEL-21</t>
@@ -4835,7 +4835,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:59.844Z</t>
+    <t>2026-07-25T15:59:48.190Z</t>
   </si>
   <si>
     <t>REP-SEL-22</t>
@@ -4849,7 +4849,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:07:59.932Z</t>
+    <t>2026-07-25T15:59:48.252Z</t>
   </si>
   <si>
     <t>REP-SEL-23</t>
@@ -4863,7 +4863,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:00.054Z</t>
+    <t>2026-07-25T15:59:48.314Z</t>
   </si>
   <si>
     <t>REP-SEL-24</t>
@@ -4877,7 +4877,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:00.141Z</t>
+    <t>2026-07-25T15:59:48.376Z</t>
   </si>
   <si>
     <t>REP-SEL-25</t>
@@ -4891,7 +4891,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:00.205Z</t>
+    <t>2026-07-25T15:59:48.438Z</t>
   </si>
   <si>
     <t>REP-SEL-26</t>
@@ -4905,7 +4905,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:00.294Z</t>
+    <t>2026-07-25T15:59:48.501Z</t>
   </si>
   <si>
     <t>REP-SEL-27</t>
@@ -4919,7 +4919,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:00.385Z</t>
+    <t>2026-07-25T15:59:48.562Z</t>
   </si>
   <si>
     <t>REP-SEL-28</t>
@@ -4933,7 +4933,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:00.468Z</t>
+    <t>2026-07-25T15:59:48.624Z</t>
   </si>
   <si>
     <t>REP-SEL-29</t>
@@ -4947,7 +4947,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:00.551Z</t>
+    <t>2026-07-25T15:59:48.699Z</t>
   </si>
   <si>
     <t>REP-SEL-30</t>
@@ -4961,7 +4961,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:00.662Z</t>
+    <t>2026-07-25T15:59:48.761Z</t>
   </si>
   <si>
     <t>REP-SEL-31</t>
@@ -4975,7 +4975,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:00.753Z</t>
+    <t>2026-07-25T15:59:48.824Z</t>
   </si>
   <si>
     <t>REP-SEL-32</t>
@@ -4989,7 +4989,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:00.836Z</t>
+    <t>2026-07-25T15:59:48.886Z</t>
   </si>
   <si>
     <t>REP-SEL-33</t>
@@ -5003,7 +5003,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:00.919Z</t>
+    <t>2026-07-25T15:59:48.946Z</t>
   </si>
   <si>
     <t>REP-SEL-34</t>
@@ -5017,7 +5017,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:01.018Z</t>
+    <t>2026-07-25T15:59:49.008Z</t>
   </si>
   <si>
     <t>REP-SEL-35</t>
@@ -5031,7 +5031,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:01.127Z</t>
+    <t>2026-07-25T15:59:49.071Z</t>
   </si>
   <si>
     <t>REP-SEL-36</t>
@@ -5045,7 +5045,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:01.225Z</t>
+    <t>2026-07-25T15:59:49.132Z</t>
   </si>
   <si>
     <t>REP-SEL-37</t>
@@ -5059,7 +5059,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:01.294Z</t>
+    <t>2026-07-25T15:59:49.193Z</t>
   </si>
   <si>
     <t>SET-SEL-01</t>
@@ -5075,7 +5075,7 @@
     <t>Settings page renders</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:01.393Z</t>
+    <t>2026-07-25T15:59:49.269Z</t>
   </si>
   <si>
     <t>SET-SEL-02</t>
@@ -5090,7 +5090,7 @@
     <t>User profile info is displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:01.468Z</t>
+    <t>2026-07-25T15:59:49.329Z</t>
   </si>
   <si>
     <t>SET-SEL-03</t>
@@ -5106,7 +5106,7 @@
     <t>Toggle switches state on click</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:01.594Z</t>
+    <t>2026-07-25T15:59:49.389Z</t>
   </si>
   <si>
     <t>SET-SEL-04</t>
@@ -5122,7 +5122,7 @@
     <t>Push toggle is functional</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:01.655Z</t>
+    <t>2026-07-25T15:59:49.451Z</t>
   </si>
   <si>
     <t>SET-SEL-05</t>
@@ -5138,7 +5138,7 @@
     <t>AI insights toggle functional</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:01.732Z</t>
+    <t>2026-07-25T15:59:49.513Z</t>
   </si>
   <si>
     <t>SET-SEL-06</t>
@@ -5154,7 +5154,7 @@
     <t>2FA toggle functional</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:01.801Z</t>
+    <t>2026-07-25T15:59:49.575Z</t>
   </si>
   <si>
     <t>SET-SEL-07</t>
@@ -5170,7 +5170,7 @@
     <t>Password reset snackbar displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:01.912Z</t>
+    <t>2026-07-25T15:59:49.635Z</t>
   </si>
   <si>
     <t>SET-SEL-08</t>
@@ -5187,7 +5187,7 @@
     <t>Language selection works</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:02.023Z</t>
+    <t>2026-07-25T15:59:49.696Z</t>
   </si>
   <si>
     <t>SET-SEL-09</t>
@@ -5204,7 +5204,7 @@
     <t>Timezone selection works</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:02.127Z</t>
+    <t>2026-07-25T15:59:49.756Z</t>
   </si>
   <si>
     <t>SET-SEL-10</t>
@@ -5220,7 +5220,7 @@
     <t>User signed out and /login loaded</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:02.219Z</t>
+    <t>2026-07-25T15:59:49.818Z</t>
   </si>
   <si>
     <t>SET-SEL-11</t>
@@ -5235,7 +5235,7 @@
     <t>App version is displayed as 1.0.0</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:02.329Z</t>
+    <t>2026-07-25T15:59:49.879Z</t>
   </si>
   <si>
     <t>SET-SEL-12</t>
@@ -5251,7 +5251,7 @@
     <t>Settings is mobile-responsive</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:02.440Z</t>
+    <t>2026-07-25T15:59:49.941Z</t>
   </si>
   <si>
     <t>SET-SEL-13</t>
@@ -5265,7 +5265,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:02.551Z</t>
+    <t>2026-07-25T15:59:50.004Z</t>
   </si>
   <si>
     <t>SET-SEL-14</t>
@@ -5279,7 +5279,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:02.656Z</t>
+    <t>2026-07-25T15:59:50.064Z</t>
   </si>
   <si>
     <t>SET-SEL-15</t>
@@ -5293,7 +5293,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:02.739Z</t>
+    <t>2026-07-25T15:59:50.126Z</t>
   </si>
   <si>
     <t>SET-SEL-16</t>
@@ -5307,7 +5307,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:02.836Z</t>
+    <t>2026-07-25T15:59:50.188Z</t>
   </si>
   <si>
     <t>SET-SEL-17</t>
@@ -5321,7 +5321,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:02.947Z</t>
+    <t>2026-07-25T15:59:50.265Z</t>
   </si>
   <si>
     <t>SET-SEL-18</t>
@@ -5335,7 +5335,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:03.051Z</t>
+    <t>2026-07-25T15:59:50.327Z</t>
   </si>
   <si>
     <t>SET-SEL-19</t>
@@ -5349,7 +5349,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:03.162Z</t>
+    <t>2026-07-25T15:59:50.390Z</t>
   </si>
   <si>
     <t>SET-SEL-20</t>
@@ -5363,7 +5363,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:03.267Z</t>
+    <t>2026-07-25T15:59:50.452Z</t>
   </si>
   <si>
     <t>SET-SEL-21</t>
@@ -5377,7 +5377,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:03.385Z</t>
+    <t>2026-07-25T15:59:50.528Z</t>
   </si>
   <si>
     <t>SET-SEL-22</t>
@@ -5391,7 +5391,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:03.497Z</t>
+    <t>2026-07-25T15:59:50.589Z</t>
   </si>
   <si>
     <t>SET-SEL-23</t>
@@ -5405,7 +5405,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:03.621Z</t>
+    <t>2026-07-25T15:59:50.665Z</t>
   </si>
   <si>
     <t>SET-SEL-24</t>
@@ -5419,7 +5419,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:03.731Z</t>
+    <t>2026-07-25T15:59:50.725Z</t>
   </si>
   <si>
     <t>SET-SEL-25</t>
@@ -5433,7 +5433,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:03.864Z</t>
+    <t>2026-07-25T15:59:50.804Z</t>
   </si>
   <si>
     <t>SET-SEL-26</t>
@@ -5447,7 +5447,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:03.968Z</t>
+    <t>2026-07-25T15:59:50.866Z</t>
   </si>
   <si>
     <t>SET-SEL-27</t>
@@ -5461,7 +5461,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:04.093Z</t>
+    <t>2026-07-25T15:59:50.930Z</t>
   </si>
   <si>
     <t>SET-SEL-28</t>
@@ -5475,7 +5475,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:04.204Z</t>
+    <t>2026-07-25T15:59:50.995Z</t>
   </si>
   <si>
     <t>SET-SEL-29</t>
@@ -5489,7 +5489,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:04.308Z</t>
+    <t>2026-07-25T15:59:51.099Z</t>
   </si>
   <si>
     <t>SET-SEL-30</t>
@@ -5503,7 +5503,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:04.433Z</t>
+    <t>2026-07-25T15:59:51.161Z</t>
   </si>
   <si>
     <t>SET-SEL-31</t>
@@ -5517,7 +5517,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:04.558Z</t>
+    <t>2026-07-25T15:59:51.223Z</t>
   </si>
   <si>
     <t>SET-SEL-32</t>
@@ -5531,7 +5531,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:04.676Z</t>
+    <t>2026-07-25T15:59:51.299Z</t>
   </si>
   <si>
     <t>SET-SEL-33</t>
@@ -5545,7 +5545,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:04.780Z</t>
+    <t>2026-07-25T15:59:51.375Z</t>
   </si>
   <si>
     <t>SET-SEL-34</t>
@@ -5559,7 +5559,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:04.900Z</t>
+    <t>2026-07-25T15:59:51.437Z</t>
   </si>
   <si>
     <t>SET-SEL-35</t>
@@ -5573,7 +5573,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:05.017Z</t>
+    <t>2026-07-25T15:59:51.499Z</t>
   </si>
   <si>
     <t>SET-SEL-36</t>
@@ -5587,7 +5587,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:05.121Z</t>
+    <t>2026-07-25T15:59:51.560Z</t>
   </si>
   <si>
     <t>SET-SEL-37</t>
@@ -5601,7 +5601,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:05.225Z</t>
+    <t>2026-07-25T15:59:51.637Z</t>
   </si>
   <si>
     <t>AI-SEL-01</t>
@@ -5617,7 +5617,7 @@
     <t>AI Chat page renders</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:05.344Z</t>
+    <t>2026-07-25T15:59:51.699Z</t>
   </si>
   <si>
     <t>AI-SEL-02</t>
@@ -5632,7 +5632,7 @@
     <t>Chat input is in DOM</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:05.437Z</t>
+    <t>2026-07-25T15:59:51.761Z</t>
   </si>
   <si>
     <t>AI-SEL-03</t>
@@ -5649,7 +5649,7 @@
     <t>User message is displayed in chat</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:05.560Z</t>
+    <t>2026-07-25T15:59:51.823Z</t>
   </si>
   <si>
     <t>AI-SEL-04</t>
@@ -5666,7 +5666,7 @@
     <t>AI response bubble is displayed</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:05.699Z</t>
+    <t>2026-07-25T15:59:51.885Z</t>
   </si>
   <si>
     <t>AI-SEL-05</t>
@@ -5682,7 +5682,7 @@
     <t>Input cleared post-send</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:05.801Z</t>
+    <t>2026-07-25T15:59:51.947Z</t>
   </si>
   <si>
     <t>AI-SEL-06</t>
@@ -5698,7 +5698,7 @@
     <t>Empty message is rejected</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:05.888Z</t>
+    <t>2026-07-25T15:59:52.023Z</t>
   </si>
   <si>
     <t>AI-SEL-07</t>
@@ -5713,7 +5713,7 @@
     <t>Quick prompt chips are rendered</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:06.013Z</t>
+    <t>2026-07-25T15:59:52.084Z</t>
   </si>
   <si>
     <t>AI-SEL-08</t>
@@ -5729,7 +5729,7 @@
     <t>AI Chat is mobile-responsive</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:06.101Z</t>
+    <t>2026-07-25T15:59:52.144Z</t>
   </si>
   <si>
     <t>AI-SEL-09</t>
@@ -5745,7 +5745,7 @@
     <t>Chat auto-scrolls to newest message</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:06.223Z</t>
+    <t>2026-07-25T15:59:52.205Z</t>
   </si>
   <si>
     <t>AI-SEL-10</t>
@@ -5760,7 +5760,7 @@
     <t>AI messages show Volt branding</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:06.343Z</t>
+    <t>2026-07-25T15:59:52.267Z</t>
   </si>
   <si>
     <t>AI-SEL-11</t>
@@ -5774,7 +5774,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:06.465Z</t>
+    <t>2026-07-25T15:59:52.329Z</t>
   </si>
   <si>
     <t>AI-SEL-12</t>
@@ -5788,7 +5788,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:06.581Z</t>
+    <t>2026-07-25T15:59:52.407Z</t>
   </si>
   <si>
     <t>AI-SEL-13</t>
@@ -5802,7 +5802,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:06.677Z</t>
+    <t>2026-07-25T15:59:52.467Z</t>
   </si>
   <si>
     <t>AI-SEL-14</t>
@@ -5816,7 +5816,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:06.791Z</t>
+    <t>2026-07-25T15:59:52.529Z</t>
   </si>
   <si>
     <t>AI-SEL-15</t>
@@ -5830,7 +5830,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:06.914Z</t>
+    <t>2026-07-25T15:59:52.591Z</t>
   </si>
   <si>
     <t>AI-SEL-16</t>
@@ -5844,7 +5844,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:07.039Z</t>
+    <t>2026-07-25T15:59:52.653Z</t>
   </si>
   <si>
     <t>AI-SEL-17</t>
@@ -5858,7 +5858,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:07.135Z</t>
+    <t>2026-07-25T15:59:52.714Z</t>
   </si>
   <si>
     <t>AI-SEL-18</t>
@@ -5872,7 +5872,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:07.233Z</t>
+    <t>2026-07-25T15:59:52.774Z</t>
   </si>
   <si>
     <t>AI-SEL-19</t>
@@ -5886,7 +5886,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:07.343Z</t>
+    <t>2026-07-25T15:59:52.835Z</t>
   </si>
   <si>
     <t>AI-SEL-20</t>
@@ -5900,7 +5900,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:07.454Z</t>
+    <t>2026-07-25T15:59:52.897Z</t>
   </si>
   <si>
     <t>AI-SEL-21</t>
@@ -5914,7 +5914,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:07.579Z</t>
+    <t>2026-07-25T15:59:52.975Z</t>
   </si>
   <si>
     <t>AI-SEL-22</t>
@@ -5928,7 +5928,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:07.690Z</t>
+    <t>2026-07-25T15:59:53.036Z</t>
   </si>
   <si>
     <t>AI-SEL-23</t>
@@ -5942,7 +5942,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:07.801Z</t>
+    <t>2026-07-25T15:59:53.113Z</t>
   </si>
   <si>
     <t>AI-SEL-24</t>
@@ -5956,7 +5956,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:07.900Z</t>
+    <t>2026-07-25T15:59:53.190Z</t>
   </si>
   <si>
     <t>AI-SEL-25</t>
@@ -5970,7 +5970,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:08.029Z</t>
+    <t>2026-07-25T15:59:53.267Z</t>
   </si>
   <si>
     <t>AI-SEL-26</t>
@@ -5984,7 +5984,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:08.169Z</t>
+    <t>2026-07-25T15:59:53.329Z</t>
   </si>
   <si>
     <t>AI-SEL-27</t>
@@ -5998,7 +5998,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:08.238Z</t>
+    <t>2026-07-25T15:59:53.406Z</t>
   </si>
   <si>
     <t>AI-SEL-28</t>
@@ -6012,7 +6012,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:08.336Z</t>
+    <t>2026-07-25T15:59:53.481Z</t>
   </si>
   <si>
     <t>AI-SEL-29</t>
@@ -6026,7 +6026,7 @@
 3. Verify Functional response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:08.448Z</t>
+    <t>2026-07-25T15:59:53.544Z</t>
   </si>
   <si>
     <t>AI-SEL-30</t>
@@ -6040,7 +6040,7 @@
 3. Verify Validation response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:08.579Z</t>
+    <t>2026-07-25T15:59:53.623Z</t>
   </si>
   <si>
     <t>AI-SEL-31</t>
@@ -6054,7 +6054,7 @@
 3. Verify Responsive response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:08.691Z</t>
+    <t>2026-07-25T15:59:53.700Z</t>
   </si>
   <si>
     <t>AI-SEL-32</t>
@@ -6068,7 +6068,7 @@
 3. Verify Performance response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:08.795Z</t>
+    <t>2026-07-25T15:59:53.777Z</t>
   </si>
   <si>
     <t>AI-SEL-33</t>
@@ -6082,7 +6082,7 @@
 3. Verify Security response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:08.912Z</t>
+    <t>2026-07-25T15:59:53.855Z</t>
   </si>
   <si>
     <t>AI-SEL-34</t>
@@ -6096,7 +6096,7 @@
 3. Verify Accessibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:09.024Z</t>
+    <t>2026-07-25T15:59:53.933Z</t>
   </si>
   <si>
     <t>AI-SEL-35</t>
@@ -6110,7 +6110,7 @@
 3. Verify UI Visibility response.</t>
   </si>
   <si>
-    <t>2026-07-23T04:08:09.142Z</t>
+    <t>2026-07-25T15:59:54.009Z</t>
   </si>
 </sst>
 </file>
@@ -6958,7 +6958,7 @@
         <v>6</v>
       </c>
       <c r="J2" s="4">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>42</v>
@@ -6996,7 +6996,7 @@
         <v>6</v>
       </c>
       <c r="J3" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>49</v>
@@ -7034,7 +7034,7 @@
         <v>6</v>
       </c>
       <c r="J4" s="4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>55</v>
@@ -7072,7 +7072,7 @@
         <v>6</v>
       </c>
       <c r="J5" s="4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>60</v>
@@ -7110,7 +7110,7 @@
         <v>6</v>
       </c>
       <c r="J6" s="4">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>65</v>
@@ -7186,7 +7186,7 @@
         <v>6</v>
       </c>
       <c r="J8" s="4">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>77</v>
@@ -7224,7 +7224,7 @@
         <v>6</v>
       </c>
       <c r="J9" s="4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>82</v>
@@ -7262,7 +7262,7 @@
         <v>6</v>
       </c>
       <c r="J10" s="4">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>88</v>
@@ -7300,7 +7300,7 @@
         <v>6</v>
       </c>
       <c r="J11" s="4">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>93</v>
@@ -7338,7 +7338,7 @@
         <v>6</v>
       </c>
       <c r="J12" s="4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>98</v>
@@ -7376,7 +7376,7 @@
         <v>6</v>
       </c>
       <c r="J13" s="4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>104</v>
@@ -7414,7 +7414,7 @@
         <v>6</v>
       </c>
       <c r="J14" s="4">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>110</v>
@@ -7452,7 +7452,7 @@
         <v>6</v>
       </c>
       <c r="J15" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>115</v>
@@ -7490,7 +7490,7 @@
         <v>6</v>
       </c>
       <c r="J16" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>121</v>
@@ -7528,7 +7528,7 @@
         <v>6</v>
       </c>
       <c r="J17" s="4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>127</v>
@@ -7566,7 +7566,7 @@
         <v>6</v>
       </c>
       <c r="J18" s="4">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>133</v>
@@ -7604,7 +7604,7 @@
         <v>6</v>
       </c>
       <c r="J19" s="4">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>138</v>
@@ -7642,7 +7642,7 @@
         <v>6</v>
       </c>
       <c r="J20" s="4">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>143</v>
@@ -7680,7 +7680,7 @@
         <v>6</v>
       </c>
       <c r="J21" s="4">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>148</v>
@@ -7718,7 +7718,7 @@
         <v>6</v>
       </c>
       <c r="J22" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>153</v>
@@ -7756,7 +7756,7 @@
         <v>6</v>
       </c>
       <c r="J23" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>158</v>
@@ -7794,7 +7794,7 @@
         <v>6</v>
       </c>
       <c r="J24" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>163</v>
@@ -7832,7 +7832,7 @@
         <v>6</v>
       </c>
       <c r="J25" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>168</v>
@@ -7870,7 +7870,7 @@
         <v>6</v>
       </c>
       <c r="J26" s="4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>173</v>
@@ -7908,7 +7908,7 @@
         <v>6</v>
       </c>
       <c r="J27" s="4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>178</v>
@@ -7946,7 +7946,7 @@
         <v>6</v>
       </c>
       <c r="J28" s="4">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K28" s="4" t="s">
         <v>183</v>
@@ -8022,7 +8022,7 @@
         <v>6</v>
       </c>
       <c r="J30" s="4">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>193</v>
@@ -8060,7 +8060,7 @@
         <v>6</v>
       </c>
       <c r="J31" s="4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>198</v>
@@ -8098,7 +8098,7 @@
         <v>6</v>
       </c>
       <c r="J32" s="4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>203</v>
@@ -8136,7 +8136,7 @@
         <v>6</v>
       </c>
       <c r="J33" s="4">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>208</v>
@@ -8174,7 +8174,7 @@
         <v>6</v>
       </c>
       <c r="J34" s="4">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>213</v>
@@ -8212,7 +8212,7 @@
         <v>6</v>
       </c>
       <c r="J35" s="4">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>218</v>
@@ -8250,7 +8250,7 @@
         <v>6</v>
       </c>
       <c r="J36" s="4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>223</v>
@@ -8326,7 +8326,7 @@
         <v>6</v>
       </c>
       <c r="J38" s="4">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>233</v>
@@ -8364,7 +8364,7 @@
         <v>6</v>
       </c>
       <c r="J39" s="4">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>238</v>
@@ -8402,7 +8402,7 @@
         <v>6</v>
       </c>
       <c r="J40" s="4">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>243</v>
@@ -8440,7 +8440,7 @@
         <v>6</v>
       </c>
       <c r="J41" s="4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>248</v>
@@ -8478,7 +8478,7 @@
         <v>6</v>
       </c>
       <c r="J42" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K42" s="4" t="s">
         <v>253</v>
@@ -8516,7 +8516,7 @@
         <v>6</v>
       </c>
       <c r="J43" s="4">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>258</v>
@@ -8554,7 +8554,7 @@
         <v>6</v>
       </c>
       <c r="J44" s="4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>263</v>
@@ -8630,7 +8630,7 @@
         <v>6</v>
       </c>
       <c r="J46" s="4">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K46" s="4" t="s">
         <v>273</v>
@@ -8668,7 +8668,7 @@
         <v>6</v>
       </c>
       <c r="J47" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K47" s="4" t="s">
         <v>278</v>
@@ -8706,7 +8706,7 @@
         <v>6</v>
       </c>
       <c r="J48" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K48" s="4" t="s">
         <v>282</v>
@@ -8744,7 +8744,7 @@
         <v>6</v>
       </c>
       <c r="J49" s="4">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K49" s="4" t="s">
         <v>286</v>
@@ -8820,7 +8820,7 @@
         <v>6</v>
       </c>
       <c r="J51" s="4">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="K51" s="4" t="s">
         <v>294</v>
@@ -8858,7 +8858,7 @@
         <v>6</v>
       </c>
       <c r="J52" s="4">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K52" s="4" t="s">
         <v>298</v>
@@ -8896,7 +8896,7 @@
         <v>6</v>
       </c>
       <c r="J53" s="4">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K53" s="4" t="s">
         <v>302</v>
@@ -8934,7 +8934,7 @@
         <v>6</v>
       </c>
       <c r="J54" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K54" s="4" t="s">
         <v>306</v>
@@ -8972,7 +8972,7 @@
         <v>6</v>
       </c>
       <c r="J55" s="4">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K55" s="4" t="s">
         <v>310</v>
@@ -9010,7 +9010,7 @@
         <v>6</v>
       </c>
       <c r="J56" s="4">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K56" s="4" t="s">
         <v>314</v>
@@ -9048,7 +9048,7 @@
         <v>6</v>
       </c>
       <c r="J57" s="4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K57" s="4" t="s">
         <v>318</v>
@@ -9086,7 +9086,7 @@
         <v>6</v>
       </c>
       <c r="J58" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K58" s="4" t="s">
         <v>322</v>
@@ -9124,7 +9124,7 @@
         <v>6</v>
       </c>
       <c r="J59" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K59" s="4" t="s">
         <v>326</v>
@@ -9162,7 +9162,7 @@
         <v>6</v>
       </c>
       <c r="J60" s="4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K60" s="4" t="s">
         <v>330</v>
@@ -9200,7 +9200,7 @@
         <v>6</v>
       </c>
       <c r="J61" s="4">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K61" s="4" t="s">
         <v>334</v>
@@ -9238,7 +9238,7 @@
         <v>6</v>
       </c>
       <c r="J62" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K62" s="4" t="s">
         <v>338</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="J63" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K63" s="4" t="s">
         <v>342</v>
@@ -9314,7 +9314,7 @@
         <v>6</v>
       </c>
       <c r="J64" s="4">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="K64" s="4" t="s">
         <v>346</v>
@@ -9352,7 +9352,7 @@
         <v>6</v>
       </c>
       <c r="J65" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K65" s="4" t="s">
         <v>350</v>
@@ -9390,7 +9390,7 @@
         <v>6</v>
       </c>
       <c r="J66" s="4">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K66" s="4" t="s">
         <v>354</v>
@@ -9428,7 +9428,7 @@
         <v>6</v>
       </c>
       <c r="J67" s="4">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K67" s="4" t="s">
         <v>358</v>
@@ -9466,7 +9466,7 @@
         <v>6</v>
       </c>
       <c r="J68" s="4">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K68" s="4" t="s">
         <v>362</v>
@@ -9504,7 +9504,7 @@
         <v>6</v>
       </c>
       <c r="J69" s="4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K69" s="4" t="s">
         <v>366</v>
@@ -9580,7 +9580,7 @@
         <v>6</v>
       </c>
       <c r="J71" s="4">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K71" s="4" t="s">
         <v>374</v>
@@ -9618,7 +9618,7 @@
         <v>6</v>
       </c>
       <c r="J72" s="4">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K72" s="4" t="s">
         <v>378</v>
@@ -9656,7 +9656,7 @@
         <v>6</v>
       </c>
       <c r="J73" s="4">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K73" s="4" t="s">
         <v>382</v>
@@ -9694,7 +9694,7 @@
         <v>6</v>
       </c>
       <c r="J74" s="4">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K74" s="4" t="s">
         <v>387</v>
@@ -9732,7 +9732,7 @@
         <v>6</v>
       </c>
       <c r="J75" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K75" s="4" t="s">
         <v>392</v>
@@ -9770,7 +9770,7 @@
         <v>6</v>
       </c>
       <c r="J76" s="4">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K76" s="4" t="s">
         <v>397</v>
@@ -9808,7 +9808,7 @@
         <v>6</v>
       </c>
       <c r="J77" s="4">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K77" s="4" t="s">
         <v>402</v>
@@ -9846,7 +9846,7 @@
         <v>6</v>
       </c>
       <c r="J78" s="4">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K78" s="4" t="s">
         <v>407</v>
@@ -9884,7 +9884,7 @@
         <v>6</v>
       </c>
       <c r="J79" s="4">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K79" s="4" t="s">
         <v>412</v>
@@ -9922,7 +9922,7 @@
         <v>6</v>
       </c>
       <c r="J80" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K80" s="4" t="s">
         <v>417</v>
@@ -9960,7 +9960,7 @@
         <v>6</v>
       </c>
       <c r="J81" s="4">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="K81" s="4" t="s">
         <v>422</v>
@@ -9998,7 +9998,7 @@
         <v>6</v>
       </c>
       <c r="J82" s="4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K82" s="4" t="s">
         <v>427</v>
@@ -10036,7 +10036,7 @@
         <v>6</v>
       </c>
       <c r="J83" s="4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K83" s="4" t="s">
         <v>432</v>
@@ -10074,7 +10074,7 @@
         <v>6</v>
       </c>
       <c r="J84" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K84" s="4" t="s">
         <v>436</v>
@@ -10112,7 +10112,7 @@
         <v>6</v>
       </c>
       <c r="J85" s="4">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K85" s="4" t="s">
         <v>440</v>
@@ -10150,7 +10150,7 @@
         <v>6</v>
       </c>
       <c r="J86" s="4">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K86" s="4" t="s">
         <v>444</v>
@@ -10226,7 +10226,7 @@
         <v>6</v>
       </c>
       <c r="J88" s="4">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K88" s="4" t="s">
         <v>452</v>
@@ -10264,7 +10264,7 @@
         <v>6</v>
       </c>
       <c r="J89" s="4">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K89" s="4" t="s">
         <v>456</v>
@@ -10302,7 +10302,7 @@
         <v>6</v>
       </c>
       <c r="J90" s="4">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="K90" s="4" t="s">
         <v>460</v>
@@ -10340,7 +10340,7 @@
         <v>6</v>
       </c>
       <c r="J91" s="4">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K91" s="4" t="s">
         <v>464</v>
@@ -10378,7 +10378,7 @@
         <v>6</v>
       </c>
       <c r="J92" s="4">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K92" s="4" t="s">
         <v>468</v>
@@ -10416,7 +10416,7 @@
         <v>6</v>
       </c>
       <c r="J93" s="4">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K93" s="4" t="s">
         <v>472</v>
@@ -10454,7 +10454,7 @@
         <v>6</v>
       </c>
       <c r="J94" s="4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K94" s="4" t="s">
         <v>476</v>
@@ -10492,7 +10492,7 @@
         <v>6</v>
       </c>
       <c r="J95" s="4">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K95" s="4" t="s">
         <v>480</v>
@@ -10530,7 +10530,7 @@
         <v>6</v>
       </c>
       <c r="J96" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K96" s="4" t="s">
         <v>484</v>
@@ -10568,7 +10568,7 @@
         <v>6</v>
       </c>
       <c r="J97" s="4">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K97" s="4" t="s">
         <v>488</v>
@@ -10606,7 +10606,7 @@
         <v>6</v>
       </c>
       <c r="J98" s="4">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K98" s="4" t="s">
         <v>492</v>
@@ -10644,7 +10644,7 @@
         <v>6</v>
       </c>
       <c r="J99" s="4">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K99" s="4" t="s">
         <v>496</v>
@@ -10682,7 +10682,7 @@
         <v>6</v>
       </c>
       <c r="J100" s="4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K100" s="4" t="s">
         <v>500</v>
@@ -10720,7 +10720,7 @@
         <v>6</v>
       </c>
       <c r="J101" s="4">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K101" s="4" t="s">
         <v>504</v>
@@ -10758,7 +10758,7 @@
         <v>6</v>
       </c>
       <c r="J102" s="4">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K102" s="4" t="s">
         <v>508</v>
@@ -10796,7 +10796,7 @@
         <v>6</v>
       </c>
       <c r="J103" s="4">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K103" s="4" t="s">
         <v>512</v>
@@ -10872,7 +10872,7 @@
         <v>6</v>
       </c>
       <c r="J105" s="4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K105" s="4" t="s">
         <v>520</v>
@@ -10910,7 +10910,7 @@
         <v>6</v>
       </c>
       <c r="J106" s="4">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K106" s="4" t="s">
         <v>524</v>
@@ -10948,7 +10948,7 @@
         <v>6</v>
       </c>
       <c r="J107" s="4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K107" s="4" t="s">
         <v>528</v>
@@ -10986,7 +10986,7 @@
         <v>6</v>
       </c>
       <c r="J108" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K108" s="4" t="s">
         <v>532</v>
@@ -11024,7 +11024,7 @@
         <v>6</v>
       </c>
       <c r="J109" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K109" s="4" t="s">
         <v>536</v>
@@ -11062,7 +11062,7 @@
         <v>6</v>
       </c>
       <c r="J110" s="4">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="K110" s="4" t="s">
         <v>541</v>
@@ -11100,7 +11100,7 @@
         <v>6</v>
       </c>
       <c r="J111" s="4">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="K111" s="4" t="s">
         <v>546</v>
@@ -11138,7 +11138,7 @@
         <v>6</v>
       </c>
       <c r="J112" s="4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K112" s="4" t="s">
         <v>551</v>
@@ -11176,7 +11176,7 @@
         <v>6</v>
       </c>
       <c r="J113" s="4">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K113" s="4" t="s">
         <v>556</v>
@@ -11214,7 +11214,7 @@
         <v>6</v>
       </c>
       <c r="J114" s="4">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K114" s="4" t="s">
         <v>561</v>
@@ -11252,7 +11252,7 @@
         <v>6</v>
       </c>
       <c r="J115" s="4">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K115" s="4" t="s">
         <v>566</v>
@@ -11290,7 +11290,7 @@
         <v>6</v>
       </c>
       <c r="J116" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K116" s="4" t="s">
         <v>571</v>
@@ -11328,7 +11328,7 @@
         <v>6</v>
       </c>
       <c r="J117" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K117" s="4" t="s">
         <v>575</v>
@@ -11366,7 +11366,7 @@
         <v>6</v>
       </c>
       <c r="J118" s="4">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K118" s="4" t="s">
         <v>579</v>
@@ -11404,7 +11404,7 @@
         <v>6</v>
       </c>
       <c r="J119" s="4">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K119" s="4" t="s">
         <v>583</v>
@@ -11442,7 +11442,7 @@
         <v>6</v>
       </c>
       <c r="J120" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K120" s="4" t="s">
         <v>587</v>
@@ -11480,7 +11480,7 @@
         <v>6</v>
       </c>
       <c r="J121" s="4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K121" s="4" t="s">
         <v>591</v>
@@ -11518,7 +11518,7 @@
         <v>6</v>
       </c>
       <c r="J122" s="4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K122" s="4" t="s">
         <v>595</v>
@@ -11632,7 +11632,7 @@
         <v>6</v>
       </c>
       <c r="J125" s="4">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K125" s="4" t="s">
         <v>607</v>
@@ -11670,7 +11670,7 @@
         <v>6</v>
       </c>
       <c r="J126" s="4">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K126" s="4" t="s">
         <v>611</v>
@@ -11708,7 +11708,7 @@
         <v>6</v>
       </c>
       <c r="J127" s="4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K127" s="4" t="s">
         <v>615</v>
@@ -11746,7 +11746,7 @@
         <v>6</v>
       </c>
       <c r="J128" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K128" s="4" t="s">
         <v>619</v>
@@ -11784,7 +11784,7 @@
         <v>6</v>
       </c>
       <c r="J129" s="4">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K129" s="4" t="s">
         <v>623</v>
@@ -11822,7 +11822,7 @@
         <v>6</v>
       </c>
       <c r="J130" s="4">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K130" s="4" t="s">
         <v>627</v>
@@ -11860,7 +11860,7 @@
         <v>6</v>
       </c>
       <c r="J131" s="4">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K131" s="4" t="s">
         <v>631</v>
@@ -11898,7 +11898,7 @@
         <v>6</v>
       </c>
       <c r="J132" s="4">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K132" s="4" t="s">
         <v>635</v>
@@ -11936,7 +11936,7 @@
         <v>6</v>
       </c>
       <c r="J133" s="4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K133" s="4" t="s">
         <v>639</v>
@@ -11974,7 +11974,7 @@
         <v>6</v>
       </c>
       <c r="J134" s="4">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K134" s="4" t="s">
         <v>643</v>
@@ -12012,7 +12012,7 @@
         <v>6</v>
       </c>
       <c r="J135" s="4">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K135" s="4" t="s">
         <v>647</v>
@@ -12050,7 +12050,7 @@
         <v>6</v>
       </c>
       <c r="J136" s="4">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K136" s="4" t="s">
         <v>651</v>
@@ -12088,7 +12088,7 @@
         <v>6</v>
       </c>
       <c r="J137" s="4">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K137" s="4" t="s">
         <v>655</v>
@@ -12126,7 +12126,7 @@
         <v>6</v>
       </c>
       <c r="J138" s="4">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K138" s="4" t="s">
         <v>659</v>
@@ -12164,7 +12164,7 @@
         <v>6</v>
       </c>
       <c r="J139" s="4">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K139" s="4" t="s">
         <v>663</v>
@@ -12240,7 +12240,7 @@
         <v>6</v>
       </c>
       <c r="J141" s="4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K141" s="4" t="s">
         <v>671</v>
@@ -12278,7 +12278,7 @@
         <v>6</v>
       </c>
       <c r="J142" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K142" s="4" t="s">
         <v>675</v>
@@ -12316,7 +12316,7 @@
         <v>6</v>
       </c>
       <c r="J143" s="4">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K143" s="4" t="s">
         <v>679</v>
@@ -12392,7 +12392,7 @@
         <v>6</v>
       </c>
       <c r="J145" s="4">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K145" s="4" t="s">
         <v>687</v>
@@ -12430,7 +12430,7 @@
         <v>6</v>
       </c>
       <c r="J146" s="4">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K146" s="4" t="s">
         <v>692</v>
@@ -12506,7 +12506,7 @@
         <v>6</v>
       </c>
       <c r="J148" s="4">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K148" s="4" t="s">
         <v>703</v>
@@ -12544,7 +12544,7 @@
         <v>6</v>
       </c>
       <c r="J149" s="4">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K149" s="4" t="s">
         <v>708</v>
@@ -12582,7 +12582,7 @@
         <v>6</v>
       </c>
       <c r="J150" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K150" s="4" t="s">
         <v>713</v>
@@ -12620,7 +12620,7 @@
         <v>6</v>
       </c>
       <c r="J151" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K151" s="4" t="s">
         <v>718</v>
@@ -12658,7 +12658,7 @@
         <v>6</v>
       </c>
       <c r="J152" s="4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K152" s="4" t="s">
         <v>723</v>
@@ -12696,7 +12696,7 @@
         <v>6</v>
       </c>
       <c r="J153" s="4">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K153" s="4" t="s">
         <v>728</v>
@@ -12734,7 +12734,7 @@
         <v>6</v>
       </c>
       <c r="J154" s="4">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K154" s="4" t="s">
         <v>733</v>
@@ -12772,7 +12772,7 @@
         <v>6</v>
       </c>
       <c r="J155" s="4">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K155" s="4" t="s">
         <v>738</v>
@@ -12810,7 +12810,7 @@
         <v>6</v>
       </c>
       <c r="J156" s="4">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="K156" s="4" t="s">
         <v>743</v>
@@ -12848,7 +12848,7 @@
         <v>6</v>
       </c>
       <c r="J157" s="4">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K157" s="4" t="s">
         <v>748</v>
@@ -12886,7 +12886,7 @@
         <v>6</v>
       </c>
       <c r="J158" s="4">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K158" s="4" t="s">
         <v>753</v>
@@ -12924,7 +12924,7 @@
         <v>6</v>
       </c>
       <c r="J159" s="4">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K159" s="4" t="s">
         <v>758</v>
@@ -13000,7 +13000,7 @@
         <v>6</v>
       </c>
       <c r="J161" s="4">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K161" s="4" t="s">
         <v>768</v>
@@ -13076,7 +13076,7 @@
         <v>6</v>
       </c>
       <c r="J163" s="4">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K163" s="4" t="s">
         <v>778</v>
@@ -13114,7 +13114,7 @@
         <v>6</v>
       </c>
       <c r="J164" s="4">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K164" s="4" t="s">
         <v>783</v>
@@ -13152,7 +13152,7 @@
         <v>6</v>
       </c>
       <c r="J165" s="4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K165" s="4" t="s">
         <v>788</v>
@@ -13190,7 +13190,7 @@
         <v>6</v>
       </c>
       <c r="J166" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K166" s="4" t="s">
         <v>792</v>
@@ -13228,7 +13228,7 @@
         <v>6</v>
       </c>
       <c r="J167" s="4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K167" s="4" t="s">
         <v>796</v>
@@ -13266,7 +13266,7 @@
         <v>6</v>
       </c>
       <c r="J168" s="4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K168" s="4" t="s">
         <v>800</v>
@@ -13304,7 +13304,7 @@
         <v>6</v>
       </c>
       <c r="J169" s="4">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K169" s="4" t="s">
         <v>804</v>
@@ -13342,7 +13342,7 @@
         <v>6</v>
       </c>
       <c r="J170" s="4">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K170" s="4" t="s">
         <v>808</v>
@@ -13380,7 +13380,7 @@
         <v>6</v>
       </c>
       <c r="J171" s="4">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K171" s="4" t="s">
         <v>812</v>
@@ -13418,7 +13418,7 @@
         <v>6</v>
       </c>
       <c r="J172" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K172" s="4" t="s">
         <v>816</v>
@@ -13456,7 +13456,7 @@
         <v>6</v>
       </c>
       <c r="J173" s="4">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="K173" s="4" t="s">
         <v>820</v>
@@ -13494,7 +13494,7 @@
         <v>6</v>
       </c>
       <c r="J174" s="4">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K174" s="4" t="s">
         <v>824</v>
@@ -13532,7 +13532,7 @@
         <v>6</v>
       </c>
       <c r="J175" s="4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K175" s="4" t="s">
         <v>828</v>
@@ -13570,7 +13570,7 @@
         <v>6</v>
       </c>
       <c r="J176" s="4">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K176" s="4" t="s">
         <v>832</v>
@@ -13608,7 +13608,7 @@
         <v>6</v>
       </c>
       <c r="J177" s="4">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K177" s="4" t="s">
         <v>836</v>
@@ -13646,7 +13646,7 @@
         <v>6</v>
       </c>
       <c r="J178" s="4">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="K178" s="4" t="s">
         <v>840</v>
@@ -13684,7 +13684,7 @@
         <v>6</v>
       </c>
       <c r="J179" s="4">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K179" s="4" t="s">
         <v>844</v>
@@ -13722,7 +13722,7 @@
         <v>6</v>
       </c>
       <c r="J180" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K180" s="4" t="s">
         <v>848</v>
@@ -13798,7 +13798,7 @@
         <v>6</v>
       </c>
       <c r="J182" s="4">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="K182" s="4" t="s">
         <v>857</v>
@@ -13836,7 +13836,7 @@
         <v>6</v>
       </c>
       <c r="J183" s="4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K183" s="4" t="s">
         <v>862</v>
@@ -13874,7 +13874,7 @@
         <v>6</v>
       </c>
       <c r="J184" s="4">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K184" s="4" t="s">
         <v>867</v>
@@ -13912,7 +13912,7 @@
         <v>6</v>
       </c>
       <c r="J185" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K185" s="4" t="s">
         <v>872</v>
@@ -13950,7 +13950,7 @@
         <v>6</v>
       </c>
       <c r="J186" s="4">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K186" s="4" t="s">
         <v>877</v>
@@ -13988,7 +13988,7 @@
         <v>6</v>
       </c>
       <c r="J187" s="4">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K187" s="4" t="s">
         <v>882</v>
@@ -14026,7 +14026,7 @@
         <v>6</v>
       </c>
       <c r="J188" s="4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K188" s="4" t="s">
         <v>887</v>
@@ -14064,7 +14064,7 @@
         <v>6</v>
       </c>
       <c r="J189" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="K189" s="4" t="s">
         <v>892</v>
@@ -14102,7 +14102,7 @@
         <v>6</v>
       </c>
       <c r="J190" s="4">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K190" s="4" t="s">
         <v>897</v>
@@ -14140,7 +14140,7 @@
         <v>6</v>
       </c>
       <c r="J191" s="4">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K191" s="4" t="s">
         <v>902</v>
@@ -14178,7 +14178,7 @@
         <v>6</v>
       </c>
       <c r="J192" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="K192" s="4" t="s">
         <v>907</v>
@@ -14216,7 +14216,7 @@
         <v>6</v>
       </c>
       <c r="J193" s="4">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K193" s="4" t="s">
         <v>912</v>
@@ -14292,7 +14292,7 @@
         <v>6</v>
       </c>
       <c r="J195" s="4">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="K195" s="4" t="s">
         <v>920</v>
@@ -14330,7 +14330,7 @@
         <v>6</v>
       </c>
       <c r="J196" s="4">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K196" s="4" t="s">
         <v>924</v>
@@ -14368,7 +14368,7 @@
         <v>6</v>
       </c>
       <c r="J197" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K197" s="4" t="s">
         <v>928</v>
@@ -14406,7 +14406,7 @@
         <v>6</v>
       </c>
       <c r="J198" s="4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K198" s="4" t="s">
         <v>932</v>
@@ -14444,7 +14444,7 @@
         <v>6</v>
       </c>
       <c r="J199" s="4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K199" s="4" t="s">
         <v>936</v>
@@ -14520,7 +14520,7 @@
         <v>6</v>
       </c>
       <c r="J201" s="4">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K201" s="4" t="s">
         <v>944</v>
@@ -14558,7 +14558,7 @@
         <v>6</v>
       </c>
       <c r="J202" s="4">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K202" s="4" t="s">
         <v>948</v>
@@ -14596,7 +14596,7 @@
         <v>6</v>
       </c>
       <c r="J203" s="4">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K203" s="4" t="s">
         <v>952</v>
@@ -14634,7 +14634,7 @@
         <v>6</v>
       </c>
       <c r="J204" s="4">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K204" s="4" t="s">
         <v>956</v>
@@ -14672,7 +14672,7 @@
         <v>6</v>
       </c>
       <c r="J205" s="4">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K205" s="4" t="s">
         <v>960</v>
@@ -14710,7 +14710,7 @@
         <v>6</v>
       </c>
       <c r="J206" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K206" s="4" t="s">
         <v>964</v>
@@ -14786,7 +14786,7 @@
         <v>6</v>
       </c>
       <c r="J208" s="4">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K208" s="4" t="s">
         <v>972</v>
@@ -14824,7 +14824,7 @@
         <v>6</v>
       </c>
       <c r="J209" s="4">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K209" s="4" t="s">
         <v>976</v>
@@ -14862,7 +14862,7 @@
         <v>6</v>
       </c>
       <c r="J210" s="4">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K210" s="4" t="s">
         <v>980</v>
@@ -14900,7 +14900,7 @@
         <v>6</v>
       </c>
       <c r="J211" s="4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K211" s="4" t="s">
         <v>984</v>
@@ -14938,7 +14938,7 @@
         <v>6</v>
       </c>
       <c r="J212" s="4">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K212" s="4" t="s">
         <v>988</v>
@@ -14976,7 +14976,7 @@
         <v>6</v>
       </c>
       <c r="J213" s="4">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="K213" s="4" t="s">
         <v>992</v>
@@ -15014,7 +15014,7 @@
         <v>6</v>
       </c>
       <c r="J214" s="4">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K214" s="4" t="s">
         <v>996</v>
@@ -15052,7 +15052,7 @@
         <v>6</v>
       </c>
       <c r="J215" s="4">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K215" s="4" t="s">
         <v>1000</v>
@@ -15090,7 +15090,7 @@
         <v>6</v>
       </c>
       <c r="J216" s="4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K216" s="4" t="s">
         <v>1004</v>
@@ -15128,7 +15128,7 @@
         <v>6</v>
       </c>
       <c r="J217" s="4">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="K217" s="4" t="s">
         <v>1008</v>
@@ -15204,7 +15204,7 @@
         <v>6</v>
       </c>
       <c r="J219" s="4">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K219" s="4" t="s">
         <v>1018</v>
@@ -15242,7 +15242,7 @@
         <v>6</v>
       </c>
       <c r="J220" s="4">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K220" s="4" t="s">
         <v>1023</v>
@@ -15280,7 +15280,7 @@
         <v>6</v>
       </c>
       <c r="J221" s="4">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K221" s="4" t="s">
         <v>1028</v>
@@ -15318,7 +15318,7 @@
         <v>6</v>
       </c>
       <c r="J222" s="4">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K222" s="4" t="s">
         <v>1033</v>
@@ -15356,7 +15356,7 @@
         <v>6</v>
       </c>
       <c r="J223" s="4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K223" s="4" t="s">
         <v>1038</v>
@@ -15394,7 +15394,7 @@
         <v>6</v>
       </c>
       <c r="J224" s="4">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K224" s="4" t="s">
         <v>1043</v>
@@ -15432,7 +15432,7 @@
         <v>6</v>
       </c>
       <c r="J225" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K225" s="4" t="s">
         <v>1048</v>
@@ -15470,7 +15470,7 @@
         <v>6</v>
       </c>
       <c r="J226" s="4">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K226" s="4" t="s">
         <v>1053</v>
@@ -15508,7 +15508,7 @@
         <v>6</v>
       </c>
       <c r="J227" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K227" s="4" t="s">
         <v>1058</v>
@@ -15546,7 +15546,7 @@
         <v>6</v>
       </c>
       <c r="J228" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K228" s="4" t="s">
         <v>1063</v>
@@ -15584,7 +15584,7 @@
         <v>6</v>
       </c>
       <c r="J229" s="4">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K229" s="4" t="s">
         <v>1068</v>
@@ -15622,7 +15622,7 @@
         <v>6</v>
       </c>
       <c r="J230" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K230" s="4" t="s">
         <v>1073</v>
@@ -15660,7 +15660,7 @@
         <v>6</v>
       </c>
       <c r="J231" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K231" s="4" t="s">
         <v>1078</v>
@@ -15698,7 +15698,7 @@
         <v>6</v>
       </c>
       <c r="J232" s="4">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K232" s="4" t="s">
         <v>1083</v>
@@ -15736,7 +15736,7 @@
         <v>6</v>
       </c>
       <c r="J233" s="4">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K233" s="4" t="s">
         <v>1088</v>
@@ -15774,7 +15774,7 @@
         <v>6</v>
       </c>
       <c r="J234" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K234" s="4" t="s">
         <v>1092</v>
@@ -15812,7 +15812,7 @@
         <v>6</v>
       </c>
       <c r="J235" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K235" s="4" t="s">
         <v>1096</v>
@@ -15850,7 +15850,7 @@
         <v>6</v>
       </c>
       <c r="J236" s="4">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K236" s="4" t="s">
         <v>1100</v>
@@ -15888,7 +15888,7 @@
         <v>6</v>
       </c>
       <c r="J237" s="4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K237" s="4" t="s">
         <v>1104</v>
@@ -15926,7 +15926,7 @@
         <v>6</v>
       </c>
       <c r="J238" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K238" s="4" t="s">
         <v>1108</v>
@@ -15964,7 +15964,7 @@
         <v>6</v>
       </c>
       <c r="J239" s="4">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K239" s="4" t="s">
         <v>1112</v>
@@ -16002,7 +16002,7 @@
         <v>6</v>
       </c>
       <c r="J240" s="4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K240" s="4" t="s">
         <v>1116</v>
@@ -16040,7 +16040,7 @@
         <v>6</v>
       </c>
       <c r="J241" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K241" s="4" t="s">
         <v>1120</v>
@@ -16078,7 +16078,7 @@
         <v>6</v>
       </c>
       <c r="J242" s="4">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K242" s="4" t="s">
         <v>1124</v>
@@ -16116,7 +16116,7 @@
         <v>6</v>
       </c>
       <c r="J243" s="4">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K243" s="4" t="s">
         <v>1128</v>
@@ -16154,7 +16154,7 @@
         <v>6</v>
       </c>
       <c r="J244" s="4">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K244" s="4" t="s">
         <v>1132</v>
@@ -16192,7 +16192,7 @@
         <v>6</v>
       </c>
       <c r="J245" s="4">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K245" s="4" t="s">
         <v>1136</v>
@@ -16230,7 +16230,7 @@
         <v>6</v>
       </c>
       <c r="J246" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K246" s="4" t="s">
         <v>1140</v>
@@ -16268,7 +16268,7 @@
         <v>6</v>
       </c>
       <c r="J247" s="4">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K247" s="4" t="s">
         <v>1144</v>
@@ -16306,7 +16306,7 @@
         <v>6</v>
       </c>
       <c r="J248" s="4">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K248" s="4" t="s">
         <v>1148</v>
@@ -16344,7 +16344,7 @@
         <v>6</v>
       </c>
       <c r="J249" s="4">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K249" s="4" t="s">
         <v>1152</v>
@@ -16382,7 +16382,7 @@
         <v>6</v>
       </c>
       <c r="J250" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K250" s="4" t="s">
         <v>1156</v>
@@ -16420,7 +16420,7 @@
         <v>6</v>
       </c>
       <c r="J251" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K251" s="4" t="s">
         <v>1160</v>
@@ -16458,7 +16458,7 @@
         <v>6</v>
       </c>
       <c r="J252" s="4">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K252" s="4" t="s">
         <v>1164</v>
@@ -16496,7 +16496,7 @@
         <v>6</v>
       </c>
       <c r="J253" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K253" s="4" t="s">
         <v>1168</v>
@@ -16534,7 +16534,7 @@
         <v>6</v>
       </c>
       <c r="J254" s="4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K254" s="4" t="s">
         <v>1172</v>
@@ -16572,7 +16572,7 @@
         <v>6</v>
       </c>
       <c r="J255" s="4">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K255" s="4" t="s">
         <v>1176</v>
@@ -16610,7 +16610,7 @@
         <v>6</v>
       </c>
       <c r="J256" s="4">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K256" s="4" t="s">
         <v>1181</v>
@@ -16648,7 +16648,7 @@
         <v>6</v>
       </c>
       <c r="J257" s="4">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K257" s="4" t="s">
         <v>1186</v>
@@ -16686,7 +16686,7 @@
         <v>6</v>
       </c>
       <c r="J258" s="4">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K258" s="4" t="s">
         <v>1191</v>
@@ -16724,7 +16724,7 @@
         <v>6</v>
       </c>
       <c r="J259" s="4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K259" s="4" t="s">
         <v>1196</v>
@@ -16762,7 +16762,7 @@
         <v>6</v>
       </c>
       <c r="J260" s="4">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K260" s="4" t="s">
         <v>1201</v>
@@ -16800,7 +16800,7 @@
         <v>6</v>
       </c>
       <c r="J261" s="4">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K261" s="4" t="s">
         <v>1206</v>
@@ -16838,7 +16838,7 @@
         <v>6</v>
       </c>
       <c r="J262" s="4">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K262" s="4" t="s">
         <v>1211</v>
@@ -16876,7 +16876,7 @@
         <v>6</v>
       </c>
       <c r="J263" s="4">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K263" s="4" t="s">
         <v>1216</v>
@@ -16914,7 +16914,7 @@
         <v>6</v>
       </c>
       <c r="J264" s="4">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K264" s="4" t="s">
         <v>1221</v>
@@ -16952,7 +16952,7 @@
         <v>6</v>
       </c>
       <c r="J265" s="4">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K265" s="4" t="s">
         <v>1226</v>
@@ -16990,7 +16990,7 @@
         <v>6</v>
       </c>
       <c r="J266" s="4">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K266" s="4" t="s">
         <v>1231</v>
@@ -17028,7 +17028,7 @@
         <v>6</v>
       </c>
       <c r="J267" s="4">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K267" s="4" t="s">
         <v>1235</v>
@@ -17066,7 +17066,7 @@
         <v>6</v>
       </c>
       <c r="J268" s="4">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K268" s="4" t="s">
         <v>1239</v>
@@ -17104,7 +17104,7 @@
         <v>6</v>
       </c>
       <c r="J269" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K269" s="4" t="s">
         <v>1243</v>
@@ -17142,7 +17142,7 @@
         <v>6</v>
       </c>
       <c r="J270" s="4">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="K270" s="4" t="s">
         <v>1247</v>
@@ -17180,7 +17180,7 @@
         <v>6</v>
       </c>
       <c r="J271" s="4">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K271" s="4" t="s">
         <v>1251</v>
@@ -17218,7 +17218,7 @@
         <v>6</v>
       </c>
       <c r="J272" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K272" s="4" t="s">
         <v>1255</v>
@@ -17256,7 +17256,7 @@
         <v>6</v>
       </c>
       <c r="J273" s="4">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K273" s="4" t="s">
         <v>1259</v>
@@ -17294,7 +17294,7 @@
         <v>6</v>
       </c>
       <c r="J274" s="4">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K274" s="4" t="s">
         <v>1263</v>
@@ -17332,7 +17332,7 @@
         <v>6</v>
       </c>
       <c r="J275" s="4">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K275" s="4" t="s">
         <v>1267</v>
@@ -17370,7 +17370,7 @@
         <v>6</v>
       </c>
       <c r="J276" s="4">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K276" s="4" t="s">
         <v>1271</v>
@@ -17408,7 +17408,7 @@
         <v>6</v>
       </c>
       <c r="J277" s="4">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K277" s="4" t="s">
         <v>1275</v>
@@ -17446,7 +17446,7 @@
         <v>6</v>
       </c>
       <c r="J278" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K278" s="4" t="s">
         <v>1279</v>
@@ -17484,7 +17484,7 @@
         <v>6</v>
       </c>
       <c r="J279" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K279" s="4" t="s">
         <v>1283</v>
@@ -17522,7 +17522,7 @@
         <v>6</v>
       </c>
       <c r="J280" s="4">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="K280" s="4" t="s">
         <v>1287</v>
@@ -17560,7 +17560,7 @@
         <v>6</v>
       </c>
       <c r="J281" s="4">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K281" s="4" t="s">
         <v>1291</v>
@@ -17598,7 +17598,7 @@
         <v>6</v>
       </c>
       <c r="J282" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K282" s="4" t="s">
         <v>1295</v>
@@ -17636,7 +17636,7 @@
         <v>6</v>
       </c>
       <c r="J283" s="4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K283" s="4" t="s">
         <v>1299</v>
@@ -17674,7 +17674,7 @@
         <v>6</v>
       </c>
       <c r="J284" s="4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K284" s="4" t="s">
         <v>1303</v>
@@ -17712,7 +17712,7 @@
         <v>6</v>
       </c>
       <c r="J285" s="4">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K285" s="4" t="s">
         <v>1307</v>
@@ -17750,7 +17750,7 @@
         <v>6</v>
       </c>
       <c r="J286" s="4">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K286" s="4" t="s">
         <v>1311</v>
@@ -17788,7 +17788,7 @@
         <v>6</v>
       </c>
       <c r="J287" s="4">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K287" s="4" t="s">
         <v>1315</v>
@@ -17826,7 +17826,7 @@
         <v>6</v>
       </c>
       <c r="J288" s="4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K288" s="4" t="s">
         <v>1319</v>
@@ -17864,7 +17864,7 @@
         <v>6</v>
       </c>
       <c r="J289" s="4">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K289" s="4" t="s">
         <v>1323</v>
@@ -17902,7 +17902,7 @@
         <v>6</v>
       </c>
       <c r="J290" s="4">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K290" s="4" t="s">
         <v>1327</v>
@@ -17940,7 +17940,7 @@
         <v>6</v>
       </c>
       <c r="J291" s="4">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K291" s="4" t="s">
         <v>1331</v>
@@ -17978,7 +17978,7 @@
         <v>6</v>
       </c>
       <c r="J292" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K292" s="4" t="s">
         <v>1335</v>
@@ -18016,7 +18016,7 @@
         <v>6</v>
       </c>
       <c r="J293" s="4">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K293" s="4" t="s">
         <v>1340</v>
@@ -18054,7 +18054,7 @@
         <v>6</v>
       </c>
       <c r="J294" s="4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K294" s="4" t="s">
         <v>1345</v>
@@ -18092,7 +18092,7 @@
         <v>6</v>
       </c>
       <c r="J295" s="4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K295" s="4" t="s">
         <v>1350</v>
@@ -18130,7 +18130,7 @@
         <v>6</v>
       </c>
       <c r="J296" s="4">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K296" s="4" t="s">
         <v>1355</v>
@@ -18168,7 +18168,7 @@
         <v>6</v>
       </c>
       <c r="J297" s="4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K297" s="4" t="s">
         <v>1360</v>
@@ -18206,7 +18206,7 @@
         <v>6</v>
       </c>
       <c r="J298" s="4">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K298" s="4" t="s">
         <v>1365</v>
@@ -18244,7 +18244,7 @@
         <v>6</v>
       </c>
       <c r="J299" s="4">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K299" s="4" t="s">
         <v>1370</v>
@@ -18282,7 +18282,7 @@
         <v>6</v>
       </c>
       <c r="J300" s="4">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K300" s="4" t="s">
         <v>1375</v>
@@ -18320,7 +18320,7 @@
         <v>6</v>
       </c>
       <c r="J301" s="4">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K301" s="4" t="s">
         <v>1379</v>
@@ -18358,7 +18358,7 @@
         <v>6</v>
       </c>
       <c r="J302" s="4">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K302" s="4" t="s">
         <v>1383</v>
@@ -18396,7 +18396,7 @@
         <v>6</v>
       </c>
       <c r="J303" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K303" s="4" t="s">
         <v>1387</v>
@@ -18434,7 +18434,7 @@
         <v>6</v>
       </c>
       <c r="J304" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K304" s="4" t="s">
         <v>1391</v>
@@ -18472,7 +18472,7 @@
         <v>6</v>
       </c>
       <c r="J305" s="4">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K305" s="4" t="s">
         <v>1395</v>
@@ -18510,7 +18510,7 @@
         <v>6</v>
       </c>
       <c r="J306" s="4">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K306" s="4" t="s">
         <v>1399</v>
@@ -18548,7 +18548,7 @@
         <v>6</v>
       </c>
       <c r="J307" s="4">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K307" s="4" t="s">
         <v>1403</v>
@@ -18586,7 +18586,7 @@
         <v>6</v>
       </c>
       <c r="J308" s="4">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K308" s="4" t="s">
         <v>1407</v>
@@ -18624,7 +18624,7 @@
         <v>6</v>
       </c>
       <c r="J309" s="4">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K309" s="4" t="s">
         <v>1411</v>
@@ -18662,7 +18662,7 @@
         <v>6</v>
       </c>
       <c r="J310" s="4">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K310" s="4" t="s">
         <v>1415</v>
@@ -18700,7 +18700,7 @@
         <v>6</v>
       </c>
       <c r="J311" s="4">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="K311" s="4" t="s">
         <v>1419</v>
@@ -18738,7 +18738,7 @@
         <v>6</v>
       </c>
       <c r="J312" s="4">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K312" s="4" t="s">
         <v>1423</v>
@@ -18776,7 +18776,7 @@
         <v>6</v>
       </c>
       <c r="J313" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K313" s="4" t="s">
         <v>1427</v>
@@ -18814,7 +18814,7 @@
         <v>6</v>
       </c>
       <c r="J314" s="4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K314" s="4" t="s">
         <v>1431</v>
@@ -18852,7 +18852,7 @@
         <v>6</v>
       </c>
       <c r="J315" s="4">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K315" s="4" t="s">
         <v>1435</v>
@@ -18890,7 +18890,7 @@
         <v>6</v>
       </c>
       <c r="J316" s="4">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K316" s="4" t="s">
         <v>1439</v>
@@ -18928,7 +18928,7 @@
         <v>6</v>
       </c>
       <c r="J317" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K317" s="4" t="s">
         <v>1443</v>
@@ -18966,7 +18966,7 @@
         <v>6</v>
       </c>
       <c r="J318" s="4">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K318" s="4" t="s">
         <v>1447</v>
@@ -19004,7 +19004,7 @@
         <v>6</v>
       </c>
       <c r="J319" s="4">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K319" s="4" t="s">
         <v>1451</v>
@@ -19080,7 +19080,7 @@
         <v>6</v>
       </c>
       <c r="J321" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K321" s="4" t="s">
         <v>1459</v>
@@ -19118,7 +19118,7 @@
         <v>6</v>
       </c>
       <c r="J322" s="4">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K322" s="4" t="s">
         <v>1463</v>
@@ -19156,7 +19156,7 @@
         <v>6</v>
       </c>
       <c r="J323" s="4">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K323" s="4" t="s">
         <v>1467</v>
@@ -19194,7 +19194,7 @@
         <v>6</v>
       </c>
       <c r="J324" s="4">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K324" s="4" t="s">
         <v>1471</v>
@@ -19232,7 +19232,7 @@
         <v>6</v>
       </c>
       <c r="J325" s="4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K325" s="4" t="s">
         <v>1475</v>
@@ -19270,7 +19270,7 @@
         <v>6</v>
       </c>
       <c r="J326" s="4">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K326" s="4" t="s">
         <v>1479</v>
@@ -19308,7 +19308,7 @@
         <v>6</v>
       </c>
       <c r="J327" s="4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K327" s="4" t="s">
         <v>1483</v>
@@ -19346,7 +19346,7 @@
         <v>6</v>
       </c>
       <c r="J328" s="4">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K328" s="4" t="s">
         <v>1487</v>
@@ -19384,7 +19384,7 @@
         <v>6</v>
       </c>
       <c r="J329" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K329" s="4" t="s">
         <v>1491</v>
@@ -19422,7 +19422,7 @@
         <v>6</v>
       </c>
       <c r="J330" s="4">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="K330" s="4" t="s">
         <v>1496</v>
@@ -19460,7 +19460,7 @@
         <v>6</v>
       </c>
       <c r="J331" s="4">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K331" s="4" t="s">
         <v>1501</v>
@@ -19498,7 +19498,7 @@
         <v>6</v>
       </c>
       <c r="J332" s="4">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K332" s="4" t="s">
         <v>1506</v>
@@ -19536,7 +19536,7 @@
         <v>6</v>
       </c>
       <c r="J333" s="4">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K333" s="4" t="s">
         <v>1511</v>
@@ -19574,7 +19574,7 @@
         <v>6</v>
       </c>
       <c r="J334" s="4">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K334" s="4" t="s">
         <v>1516</v>
@@ -19612,7 +19612,7 @@
         <v>6</v>
       </c>
       <c r="J335" s="4">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K335" s="4" t="s">
         <v>1521</v>
@@ -19650,7 +19650,7 @@
         <v>6</v>
       </c>
       <c r="J336" s="4">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K336" s="4" t="s">
         <v>1526</v>
@@ -19688,7 +19688,7 @@
         <v>6</v>
       </c>
       <c r="J337" s="4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K337" s="4" t="s">
         <v>1531</v>
@@ -19726,7 +19726,7 @@
         <v>6</v>
       </c>
       <c r="J338" s="4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K338" s="4" t="s">
         <v>1536</v>
@@ -19764,7 +19764,7 @@
         <v>6</v>
       </c>
       <c r="J339" s="4">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K339" s="4" t="s">
         <v>1541</v>
@@ -19802,7 +19802,7 @@
         <v>6</v>
       </c>
       <c r="J340" s="4">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K340" s="4" t="s">
         <v>1546</v>
@@ -19840,7 +19840,7 @@
         <v>6</v>
       </c>
       <c r="J341" s="4">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K341" s="4" t="s">
         <v>1551</v>
@@ -19878,7 +19878,7 @@
         <v>6</v>
       </c>
       <c r="J342" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K342" s="4" t="s">
         <v>1555</v>
@@ -19916,7 +19916,7 @@
         <v>6</v>
       </c>
       <c r="J343" s="4">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K343" s="4" t="s">
         <v>1559</v>
@@ -19954,7 +19954,7 @@
         <v>6</v>
       </c>
       <c r="J344" s="4">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K344" s="4" t="s">
         <v>1563</v>
@@ -19992,7 +19992,7 @@
         <v>6</v>
       </c>
       <c r="J345" s="4">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K345" s="4" t="s">
         <v>1567</v>
@@ -20030,7 +20030,7 @@
         <v>6</v>
       </c>
       <c r="J346" s="4">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K346" s="4" t="s">
         <v>1571</v>
@@ -20106,7 +20106,7 @@
         <v>6</v>
       </c>
       <c r="J348" s="4">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K348" s="4" t="s">
         <v>1579</v>
@@ -20144,7 +20144,7 @@
         <v>6</v>
       </c>
       <c r="J349" s="4">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="K349" s="4" t="s">
         <v>1583</v>
@@ -20182,7 +20182,7 @@
         <v>6</v>
       </c>
       <c r="J350" s="4">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K350" s="4" t="s">
         <v>1587</v>
@@ -20220,7 +20220,7 @@
         <v>6</v>
       </c>
       <c r="J351" s="4">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K351" s="4" t="s">
         <v>1591</v>
@@ -20258,7 +20258,7 @@
         <v>6</v>
       </c>
       <c r="J352" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K352" s="4" t="s">
         <v>1595</v>
@@ -20296,7 +20296,7 @@
         <v>6</v>
       </c>
       <c r="J353" s="4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K353" s="4" t="s">
         <v>1599</v>
@@ -20334,7 +20334,7 @@
         <v>6</v>
       </c>
       <c r="J354" s="4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K354" s="4" t="s">
         <v>1603</v>
@@ -20372,7 +20372,7 @@
         <v>6</v>
       </c>
       <c r="J355" s="4">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K355" s="4" t="s">
         <v>1607</v>
@@ -20410,7 +20410,7 @@
         <v>6</v>
       </c>
       <c r="J356" s="4">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K356" s="4" t="s">
         <v>1611</v>
@@ -20448,7 +20448,7 @@
         <v>6</v>
       </c>
       <c r="J357" s="4">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K357" s="4" t="s">
         <v>1615</v>
@@ -20486,7 +20486,7 @@
         <v>6</v>
       </c>
       <c r="J358" s="4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K358" s="4" t="s">
         <v>1619</v>
@@ -20524,7 +20524,7 @@
         <v>6</v>
       </c>
       <c r="J359" s="4">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K359" s="4" t="s">
         <v>1623</v>
@@ -20562,7 +20562,7 @@
         <v>6</v>
       </c>
       <c r="J360" s="4">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="K360" s="4" t="s">
         <v>1627</v>
@@ -20638,7 +20638,7 @@
         <v>6</v>
       </c>
       <c r="J362" s="4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K362" s="4" t="s">
         <v>1635</v>
@@ -20676,7 +20676,7 @@
         <v>6</v>
       </c>
       <c r="J363" s="4">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K363" s="4" t="s">
         <v>1639</v>
@@ -20714,7 +20714,7 @@
         <v>6</v>
       </c>
       <c r="J364" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K364" s="4" t="s">
         <v>1643</v>
@@ -20752,7 +20752,7 @@
         <v>6</v>
       </c>
       <c r="J365" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K365" s="4" t="s">
         <v>1647</v>
@@ -20790,7 +20790,7 @@
         <v>6</v>
       </c>
       <c r="J366" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K366" s="4" t="s">
         <v>1651</v>
@@ -20828,7 +20828,7 @@
         <v>6</v>
       </c>
       <c r="J367" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="K367" s="4" t="s">
         <v>1656</v>
@@ -20904,7 +20904,7 @@
         <v>6</v>
       </c>
       <c r="J369" s="4">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K369" s="4" t="s">
         <v>1666</v>
@@ -20942,7 +20942,7 @@
         <v>6</v>
       </c>
       <c r="J370" s="4">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K370" s="4" t="s">
         <v>1671</v>
@@ -20980,7 +20980,7 @@
         <v>6</v>
       </c>
       <c r="J371" s="4">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K371" s="4" t="s">
         <v>1676</v>
@@ -21018,7 +21018,7 @@
         <v>6</v>
       </c>
       <c r="J372" s="4">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K372" s="4" t="s">
         <v>1681</v>
@@ -21056,7 +21056,7 @@
         <v>6</v>
       </c>
       <c r="J373" s="4">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K373" s="4" t="s">
         <v>1686</v>
@@ -21094,7 +21094,7 @@
         <v>6</v>
       </c>
       <c r="J374" s="4">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K374" s="4" t="s">
         <v>1691</v>
@@ -21132,7 +21132,7 @@
         <v>6</v>
       </c>
       <c r="J375" s="4">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K375" s="4" t="s">
         <v>1696</v>
@@ -21170,7 +21170,7 @@
         <v>6</v>
       </c>
       <c r="J376" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K376" s="4" t="s">
         <v>1701</v>
@@ -21208,7 +21208,7 @@
         <v>6</v>
       </c>
       <c r="J377" s="4">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K377" s="4" t="s">
         <v>1705</v>
@@ -21246,7 +21246,7 @@
         <v>6</v>
       </c>
       <c r="J378" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K378" s="4" t="s">
         <v>1709</v>
@@ -21284,7 +21284,7 @@
         <v>6</v>
       </c>
       <c r="J379" s="4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K379" s="4" t="s">
         <v>1713</v>
@@ -21322,7 +21322,7 @@
         <v>6</v>
       </c>
       <c r="J380" s="4">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K380" s="4" t="s">
         <v>1717</v>
@@ -21360,7 +21360,7 @@
         <v>6</v>
       </c>
       <c r="J381" s="4">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K381" s="4" t="s">
         <v>1721</v>
@@ -21398,7 +21398,7 @@
         <v>6</v>
       </c>
       <c r="J382" s="4">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="K382" s="4" t="s">
         <v>1725</v>
@@ -21436,7 +21436,7 @@
         <v>6</v>
       </c>
       <c r="J383" s="4">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K383" s="4" t="s">
         <v>1729</v>
@@ -21474,7 +21474,7 @@
         <v>6</v>
       </c>
       <c r="J384" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K384" s="4" t="s">
         <v>1733</v>
@@ -21512,7 +21512,7 @@
         <v>6</v>
       </c>
       <c r="J385" s="4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K385" s="4" t="s">
         <v>1737</v>
@@ -21550,7 +21550,7 @@
         <v>6</v>
       </c>
       <c r="J386" s="4">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K386" s="4" t="s">
         <v>1741</v>
@@ -21626,7 +21626,7 @@
         <v>6</v>
       </c>
       <c r="J388" s="4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K388" s="4" t="s">
         <v>1749</v>
@@ -21664,7 +21664,7 @@
         <v>6</v>
       </c>
       <c r="J389" s="4">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K389" s="4" t="s">
         <v>1753</v>
@@ -21702,7 +21702,7 @@
         <v>6</v>
       </c>
       <c r="J390" s="4">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K390" s="4" t="s">
         <v>1757</v>
@@ -21740,7 +21740,7 @@
         <v>6</v>
       </c>
       <c r="J391" s="4">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="K391" s="4" t="s">
         <v>1761</v>
@@ -21778,7 +21778,7 @@
         <v>6</v>
       </c>
       <c r="J392" s="4">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="K392" s="4" t="s">
         <v>1765</v>
@@ -21816,7 +21816,7 @@
         <v>6</v>
       </c>
       <c r="J393" s="4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="K393" s="4" t="s">
         <v>1769</v>
@@ -21854,7 +21854,7 @@
         <v>6</v>
       </c>
       <c r="J394" s="4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K394" s="4" t="s">
         <v>1773</v>
@@ -21892,7 +21892,7 @@
         <v>6</v>
       </c>
       <c r="J395" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K395" s="4" t="s">
         <v>1777</v>
@@ -21930,7 +21930,7 @@
         <v>6</v>
       </c>
       <c r="J396" s="4">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K396" s="4" t="s">
         <v>1781</v>
@@ -21968,7 +21968,7 @@
         <v>6</v>
       </c>
       <c r="J397" s="4">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K397" s="4" t="s">
         <v>1785</v>
@@ -22006,7 +22006,7 @@
         <v>6</v>
       </c>
       <c r="J398" s="4">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="K398" s="4" t="s">
         <v>1789</v>
@@ -22044,7 +22044,7 @@
         <v>6</v>
       </c>
       <c r="J399" s="4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K399" s="4" t="s">
         <v>1793</v>
@@ -22082,7 +22082,7 @@
         <v>6</v>
       </c>
       <c r="J400" s="4">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K400" s="4" t="s">
         <v>1797</v>
@@ -22120,7 +22120,7 @@
         <v>6</v>
       </c>
       <c r="J401" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K401" s="4" t="s">
         <v>1801</v>
